--- a/src/attributions/attributions_saliency_traj_82.xlsx
+++ b/src/attributions/attributions_saliency_traj_82.xlsx
@@ -999,571 +999,571 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.0007870797999203205</v>
+        <v>4.650522189564299e-09</v>
       </c>
       <c r="B2" t="n">
-        <v>0.07945197820663452</v>
+        <v>8.847031551795226e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001816177624277771</v>
+        <v>2.538731447288001e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02101907879114151</v>
+        <v>7.630063691976829e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00752377649769187</v>
+        <v>1.27891421897175e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03410648927092552</v>
+        <v>1.414551231704309e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001625465229153633</v>
+        <v>1.098759838669139e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04312610253691673</v>
+        <v>1.828265649983507e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06370841711759567</v>
+        <v>3.252112135143648e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01381969824433327</v>
+        <v>2.213362826353205e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>0.06910479068756104</v>
+        <v>1.579548225549843e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00650339899584651</v>
+        <v>6.038556876752921e-10</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0382131040096283</v>
+        <v>7.223814435519671e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>0.002625532448291779</v>
+        <v>1.976775543255371e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>0.03071236796677113</v>
+        <v>2.282760114269422e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>0.006982441991567612</v>
+        <v>4.936627107099412e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.02382458932697773</v>
+        <v>7.296629966901946e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>0.06172576546669006</v>
+        <v>6.593132262366908e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004396730568259954</v>
+        <v>2.418682809590678e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0006485451012849808</v>
+        <v>3.226764633268431e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>0.008549630641937256</v>
+        <v>6.180970735236713e-10</v>
       </c>
       <c r="V2" t="n">
-        <v>0.006931784562766552</v>
+        <v>7.840922577884157e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>0.004431861452758312</v>
+        <v>2.714035218787103e-09</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01863704994320869</v>
+        <v>2.145039701417772e-10</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.002452295506373048</v>
+        <v>3.418470839733345e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.002081108745187521</v>
+        <v>4.83320494737427e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.002014721743762493</v>
+        <v>3.288130434597747e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.01324731018394232</v>
+        <v>2.068672788624326e-09</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.005728867836296558</v>
+        <v>4.436085720982419e-09</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.0309266708791256</v>
+        <v>4.708352818738604e-09</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.00536035792902112</v>
+        <v>1.752270506472087e-08</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.005297273397445679</v>
+        <v>9.408513967912313e-09</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.02003846131265163</v>
+        <v>3.304094331468832e-09</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.009560331702232361</v>
+        <v>1.988157860566275e-09</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.01191430352628231</v>
+        <v>6.328302770697292e-09</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.004589367657899857</v>
+        <v>6.013831654883006e-09</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.006944974884390831</v>
+        <v>2.875511384559104e-09</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.006655954290181398</v>
+        <v>2.696027845416893e-09</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.002684170147404075</v>
+        <v>1.40766909240142e-09</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.004709030501544476</v>
+        <v>2.874051219237117e-09</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.0133168138563633</v>
+        <v>5.732925689727608e-09</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.006625618319958448</v>
+        <v>4.146210930144889e-09</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.005084176547825336</v>
+        <v>5.622617482714531e-09</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.00262959604151547</v>
+        <v>2.216853589587231e-09</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.007899783551692963</v>
+        <v>2.826425316015957e-09</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.002724314574152231</v>
+        <v>1.927561665837629e-09</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.07390778511762619</v>
+        <v>2.58414996068268e-08</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.01761616766452789</v>
+        <v>3.290477057493746e-10</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.005103743635118008</v>
+        <v>3.079359656155134e-09</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.04860158264636993</v>
+        <v>9.305431092343497e-09</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.01032338850200176</v>
+        <v>5.569835703767012e-10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.01546339876949787</v>
+        <v>5.063096608637352e-09</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.01029200945049524</v>
+        <v>6.486382098103149e-09</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.01076341047883034</v>
+        <v>3.16048076598463e-09</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.009415148757398129</v>
+        <v>3.051972674583681e-09</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.002718744799494743</v>
+        <v>7.079422825739812e-09</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.00639165798202157</v>
+        <v>2.258552678213732e-09</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.00128691759891808</v>
+        <v>8.728511247113602e-09</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.004431236069649458</v>
+        <v>1.036180563573907e-08</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.04500423744320869</v>
+        <v>1.047229591932819e-08</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.002305792877450585</v>
+        <v>2.23718821246166e-09</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.01729730516672134</v>
+        <v>6.176458455797729e-09</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.05810639634728432</v>
+        <v>2.219398442804277e-09</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.009526330977678299</v>
+        <v>3.486822164333603e-09</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.002532987389713526</v>
+        <v>7.068235330365269e-09</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.00588874239474535</v>
+        <v>2.417895328399311e-10</v>
       </c>
       <c r="BO2" t="n">
-        <v>6.603053770959377e-05</v>
+        <v>1.67586389210328e-09</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.05226600542664528</v>
+        <v>6.886148540274917e-09</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.01400854997336864</v>
+        <v>3.675553417181732e-09</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.01391220651566982</v>
+        <v>1.268639149287765e-08</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.001142365857958794</v>
+        <v>3.522812930256691e-09</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.0256335660815239</v>
+        <v>3.616227983727072e-09</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.003413818776607513</v>
+        <v>9.759614227888846e-10</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.04138079285621643</v>
+        <v>1.290803997022749e-08</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.01141073368489742</v>
+        <v>5.922834445115654e-10</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.007107404060661793</v>
+        <v>4.72095251780047e-10</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.01278589759021997</v>
+        <v>1.199439392252089e-08</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.008141910657286644</v>
+        <v>7.488213382700337e-10</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.004675230011343956</v>
+        <v>3.895645139806447e-09</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.006927859503775835</v>
+        <v>4.797138686285507e-09</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.005239014513790607</v>
+        <v>3.619722299674777e-09</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.0003182881628163159</v>
+        <v>1.261438953292782e-09</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.01141121983528137</v>
+        <v>4.123862140659185e-09</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.005919243209064007</v>
+        <v>7.101304544399056e-10</v>
       </c>
       <c r="CG2" t="n">
-        <v>5.190318915992975e-06</v>
+        <v>3.875879173165231e-09</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.004739418160170317</v>
+        <v>4.01420052753565e-09</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.003431866411119699</v>
+        <v>3.499302181353414e-09</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.004257461987435818</v>
+        <v>4.960570620937688e-09</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.005243686493486166</v>
+        <v>7.227382026187001e-10</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.01746465265750885</v>
+        <v>1.118938719457674e-09</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.02006684429943562</v>
+        <v>7.079064889836673e-09</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.01580537110567093</v>
+        <v>1.660605519759883e-08</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.0005488084862008691</v>
+        <v>1.793759446533372e-10</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.02132685296237469</v>
+        <v>1.504734825630294e-08</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.03007189370691776</v>
+        <v>1.61946900334442e-08</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.01650088280439377</v>
+        <v>3.972743911617727e-09</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.01050994079560041</v>
+        <v>3.415291605080029e-09</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.03418992459774017</v>
+        <v>3.840590068193706e-09</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.01699780486524105</v>
+        <v>3.820926242070755e-09</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.0002095763920806348</v>
+        <v>2.788404618314644e-09</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.01263185311108828</v>
+        <v>3.989093499967566e-09</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.003506876062601805</v>
+        <v>4.472194836679932e-10</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.001565180718898773</v>
+        <v>2.131101961566628e-09</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.0005457195802591741</v>
+        <v>2.643499419363593e-09</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.0009584017097949982</v>
+        <v>3.865828990257114e-09</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.004218022339046001</v>
+        <v>2.85721890591617e-09</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.003321574535220861</v>
+        <v>1.67469393907993e-09</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.01331148855388165</v>
+        <v>2.391653985966968e-09</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.005934674292802811</v>
+        <v>3.428737072042054e-09</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.007792073301970959</v>
+        <v>3.141557014529894e-10</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.01212658546864986</v>
+        <v>4.379492879458269e-10</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.01876669377088547</v>
+        <v>3.198770581747112e-09</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.004609007854014635</v>
+        <v>1.578583708194969e-09</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.0004462830256670713</v>
+        <v>3.18362736173583e-09</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.005752028897404671</v>
+        <v>8.336066947833842e-09</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.03497343510389328</v>
+        <v>4.906158812545414e-12</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.002502401359379292</v>
+        <v>1.334698573884907e-09</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.002370947506278753</v>
+        <v>4.450819157675312e-10</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.004654874093830585</v>
+        <v>1.95070559705357e-09</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.004324001260101795</v>
+        <v>7.69018626556317e-10</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.006285829469561577</v>
+        <v>6.689005349613808e-09</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.01105852611362934</v>
+        <v>7.52159845518463e-09</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.00291124265640974</v>
+        <v>4.902934502837297e-09</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.009163212962448597</v>
+        <v>1.050310505235075e-08</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.0009974923450499773</v>
+        <v>6.048432421579264e-09</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.01864154450595379</v>
+        <v>4.052671087606541e-09</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.0005941077833995223</v>
+        <v>2.58875809677761e-09</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.02274872176349163</v>
+        <v>4.287139532266337e-09</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.007970775477588177</v>
+        <v>2.014826305796191e-09</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.003484120825305581</v>
+        <v>1.35584576899106e-09</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.00288950907997787</v>
+        <v>1.577542096953266e-09</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.01740150153636932</v>
+        <v>2.167292567634149e-09</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.004888248629868031</v>
+        <v>2.247624308893137e-10</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.01443164609372616</v>
+        <v>7.887559938524191e-09</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.004671518690884113</v>
+        <v>1.142714256552324e-10</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.003214484779164195</v>
+        <v>3.660197700483536e-09</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.01445772871375084</v>
+        <v>2.568600332431004e-10</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.009137634187936783</v>
+        <v>2.3559887374347e-10</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.007932958193123341</v>
+        <v>2.418870437281839e-09</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.007277189288288355</v>
+        <v>3.513990765036112e-10</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.004524600226432085</v>
+        <v>1.059174525863682e-09</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.008337803184986115</v>
+        <v>1.857165088381407e-09</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.00320660462602973</v>
+        <v>4.803847986067922e-09</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.01796742714941502</v>
+        <v>1.228497747973734e-09</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.003597622038796544</v>
+        <v>2.092173545520382e-09</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.007266150321811438</v>
+        <v>2.102176210883044e-10</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.008605857379734516</v>
+        <v>3.822433480848986e-10</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.004987467546015978</v>
+        <v>2.106600893725386e-09</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.01294988207519054</v>
+        <v>3.191889419440486e-09</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.01608450710773468</v>
+        <v>1.313136044345242e-09</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.007570783142000437</v>
+        <v>5.187250629035134e-10</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.004982460290193558</v>
+        <v>6.409913932969857e-09</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.008088963106274605</v>
+        <v>9.119311528138496e-09</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.001967349089682102</v>
+        <v>1.929590709437434e-09</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.01503351517021656</v>
+        <v>5.110069256630823e-09</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.003308847779408097</v>
+        <v>5.722166074306756e-10</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.002724714344367385</v>
+        <v>2.699113377246931e-09</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.0008527084719389677</v>
+        <v>3.258985303844497e-09</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.003781327744945884</v>
+        <v>2.186070879872659e-09</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.005095019470900297</v>
+        <v>3.005395932120791e-09</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.002956725424155593</v>
+        <v>1.558771556275929e-09</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.01397624518722296</v>
+        <v>8.513922900021953e-10</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.00419582100585103</v>
+        <v>1.578739028396114e-09</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.006809331476688385</v>
+        <v>3.174371654424135e-09</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.00458927359431982</v>
+        <v>2.018768624489908e-10</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.00759844807907939</v>
+        <v>3.711340124112894e-09</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.01962966285645962</v>
+        <v>1.973787577824737e-09</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.002934133168309927</v>
+        <v>1.877109578884983e-12</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.0005209539085626602</v>
+        <v>2.142257038428852e-09</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.006120460573583841</v>
+        <v>8.209600999009581e-09</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.0004000640765298158</v>
+        <v>1.664574256210472e-09</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.00550962844863534</v>
+        <v>3.816286398006241e-09</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.01153937727212906</v>
+        <v>7.204989049824917e-09</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.01388696394860744</v>
+        <v>7.471248619772553e-10</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.006121932063251734</v>
+        <v>4.814618481674415e-09</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.03138807788491249</v>
+        <v>5.031783878450824e-10</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.01204935926944017</v>
+        <v>2.877396765299522e-09</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.02290945500135422</v>
+        <v>5.707217809458598e-09</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.007860502228140831</v>
+        <v>4.463573066715298e-09</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.003382899565622211</v>
+        <v>2.8986262279318e-09</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.01133344043046236</v>
+        <v>9.664207212267684e-10</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.00816990714520216</v>
+        <v>2.365912465940312e-10</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.00828972365707159</v>
+        <v>9.70571178982027e-10</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.01115560717880726</v>
+        <v>2.884181782292217e-09</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.007597163319587708</v>
+        <v>5.880521625201141e-10</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.01504544448107481</v>
+        <v>5.561977989287925e-09</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.01349637657403946</v>
+        <v>6.60754917447548e-09</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.006983650848269463</v>
+        <v>8.800173922907106e-10</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.0002200508606620133</v>
+        <v>1.556548334669117e-09</v>
       </c>
     </row>
     <row r="3">
@@ -2706,571 +2706,571 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.001338416012004018</v>
+        <v>8.045926147559612e-10</v>
       </c>
       <c r="B5" t="n">
-        <v>0.02015111409127712</v>
+        <v>1.094619617170167e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002340695820748806</v>
+        <v>2.197316217866785e-10</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004192455671727657</v>
+        <v>1.719901998598061e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003983902279287577</v>
+        <v>5.184680462733127e-10</v>
       </c>
       <c r="F5" t="n">
-        <v>7.871631532907486e-05</v>
+        <v>2.651502628570057e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004022825509309769</v>
+        <v>4.333173264647883e-10</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001259326352737844</v>
+        <v>1.054821785473337e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003862274577841163</v>
+        <v>4.289486543740395e-10</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004772523418068886</v>
+        <v>7.536536394958659e-10</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01655835658311844</v>
+        <v>1.278330441500941e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002962736878544092</v>
+        <v>2.951268673889729e-10</v>
       </c>
       <c r="M5" t="n">
-        <v>0.008382877334952354</v>
+        <v>5.940278824390077e-10</v>
       </c>
       <c r="N5" t="n">
-        <v>0.006786150857806206</v>
+        <v>5.367892241814332e-10</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004773862194269896</v>
+        <v>5.609747666390774e-10</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003464877838268876</v>
+        <v>1.03775232851433e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0005764093366451561</v>
+        <v>1.204733424131632e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>0.004002577625215054</v>
+        <v>2.03045288915682e-10</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002423160243779421</v>
+        <v>3.293367245582601e-10</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004097024444490671</v>
+        <v>3.0936522787961e-10</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001309769344516098</v>
+        <v>7.46264855466805e-11</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001511992886662483</v>
+        <v>3.892053623832936e-10</v>
       </c>
       <c r="W5" t="n">
-        <v>0.003989883232861757</v>
+        <v>2.02128071224994e-11</v>
       </c>
       <c r="X5" t="n">
-        <v>0.003308197017759085</v>
+        <v>2.244232577552907e-10</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.000158715556608513</v>
+        <v>3.418284266754057e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001410227036103606</v>
+        <v>1.694112627959043e-10</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.001558179152198136</v>
+        <v>6.158571430603388e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.002538569970056415</v>
+        <v>1.103827473869501e-09</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.004222616087645292</v>
+        <v>6.736549651442658e-10</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.002839731518179178</v>
+        <v>3.583282282004774e-10</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0009950164239853621</v>
+        <v>2.487338113255078e-10</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0002555376850068569</v>
+        <v>2.23641993812862e-10</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0009876111289486289</v>
+        <v>1.495778917393054e-10</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.0009777072118595243</v>
+        <v>1.35267991252519e-10</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.003797874320298433</v>
+        <v>3.574668339112463e-10</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5.553716255235486e-05</v>
+        <v>2.373642671305021e-10</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.00206700898706913</v>
+        <v>2.848208890959825e-10</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.002215110464021564</v>
+        <v>1.635506174935131e-10</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0002965164312627167</v>
+        <v>1.170704921893417e-10</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.0009567193919792771</v>
+        <v>4.008227916241225e-10</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.000612279400229454</v>
+        <v>4.950761467448217e-10</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.0006068804068490863</v>
+        <v>1.152601208920245e-10</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.0004840529581997544</v>
+        <v>6.038335387259508e-10</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.0007035122253000736</v>
+        <v>2.033530566158959e-10</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.0008216395508497953</v>
+        <v>1.448655778668595e-10</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.00244499952532351</v>
+        <v>2.975430735130402e-10</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.01268716622143984</v>
+        <v>3.214688237829222e-11</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.002531390637159348</v>
+        <v>4.392910479822376e-10</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.003469206858426332</v>
+        <v>8.493580838653259e-11</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.001607731101103127</v>
+        <v>8.122504890906157e-10</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.0008714552968740463</v>
+        <v>4.420752930389682e-10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.005315791815519333</v>
+        <v>3.22858600965148e-10</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.0006128882523626089</v>
+        <v>7.375876576176665e-10</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.448136754333973e-05</v>
+        <v>6.371158461915272e-11</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0002519288100302219</v>
+        <v>1.53908663591551e-10</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.00602182699367404</v>
+        <v>1.550585215781553e-10</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.004844502545893192</v>
+        <v>2.971709545107615e-10</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.002661624224856496</v>
+        <v>1.84965542882054e-10</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.004581963643431664</v>
+        <v>1.056949971989241e-09</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.0006331238546408713</v>
+        <v>2.605854698689569e-10</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.00208009104244411</v>
+        <v>8.89142370841256e-11</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.0002717554452829063</v>
+        <v>9.606649503668407e-11</v>
       </c>
       <c r="BK5" t="n">
-        <v>8.679274469614029e-05</v>
+        <v>1.263300464238171e-09</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.0005435751518234611</v>
+        <v>3.737821163696253e-10</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.0006478347349911928</v>
+        <v>7.829397130620919e-10</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.001908713253214955</v>
+        <v>1.635488272588859e-10</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.001265862956643105</v>
+        <v>2.516243324812706e-10</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.004833371378481388</v>
+        <v>6.087770287876992e-10</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.001211572089232504</v>
+        <v>1.626702661461366e-10</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.002042348496615887</v>
+        <v>1.061438992255859e-10</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.00426856055855751</v>
+        <v>1.594792353731833e-11</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.001395775354467332</v>
+        <v>7.974439164559755e-11</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.0004045518580824137</v>
+        <v>3.377516599734065e-10</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.006019553635269403</v>
+        <v>1.968466223356558e-10</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.002562405541539192</v>
+        <v>2.289199385607787e-11</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.001604358199983835</v>
+        <v>4.774149478525835e-11</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.00111519789788872</v>
+        <v>6.636580174301798e-10</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.0009379579569213092</v>
+        <v>2.835729984163038e-10</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.002007908886298537</v>
+        <v>7.356406594993814e-10</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.002326647751033306</v>
+        <v>1.246855049763518e-11</v>
       </c>
       <c r="CC5" t="n">
-        <v>5.383772077038884e-05</v>
+        <v>5.385039636429667e-11</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.0004463442601263523</v>
+        <v>1.289493095635308e-10</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.004009669180959463</v>
+        <v>1.698848839382094e-10</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.00128258834592998</v>
+        <v>1.411157579678246e-10</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.0003005967009812593</v>
+        <v>1.274079869384437e-10</v>
       </c>
       <c r="CH5" t="n">
-        <v>5.176538252271712e-05</v>
+        <v>1.512428654537601e-10</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.14504509838298e-05</v>
+        <v>3.179350879789489e-11</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.001109841978177428</v>
+        <v>1.052224418707226e-10</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.0004528550780378282</v>
+        <v>6.689357401334917e-11</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.0007669529295526445</v>
+        <v>2.759471123825463e-11</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.004421570803970098</v>
+        <v>5.986714457506537e-10</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.003587394021451473</v>
+        <v>5.691879745306494e-10</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.000434586894698441</v>
+        <v>3.820521121689069e-10</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.005372974555939436</v>
+        <v>1.916264785739585e-10</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.00431086728349328</v>
+        <v>6.773056560049895e-10</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.0006824552547186613</v>
+        <v>3.14958642499974e-10</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.0003811357310041785</v>
+        <v>1.64046054518252e-10</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.0004557626089081168</v>
+        <v>6.562370646889804e-10</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.001332552288658917</v>
+        <v>5.259793711687166e-10</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.0005985685274936259</v>
+        <v>1.030580620842159e-10</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.003661823691800237</v>
+        <v>2.837104995379036e-10</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.001605923054739833</v>
+        <v>1.608518596096786e-10</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.00104118010494858</v>
+        <v>1.007282382503583e-10</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0009767492301762104</v>
+        <v>4.61823253250504e-11</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.0001958962675416842</v>
+        <v>9.043538834463405e-11</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.001425747759640217</v>
+        <v>1.228458307300784e-12</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.0002086024906020612</v>
+        <v>6.480704167755036e-11</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.001114586135372519</v>
+        <v>6.973287225431335e-11</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.00305506750009954</v>
+        <v>2.218686068200526e-10</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.0002433668414596468</v>
+        <v>6.349038517150518e-10</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.001118014217354357</v>
+        <v>8.584088995178263e-10</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.0007379094022326171</v>
+        <v>1.350174749781274e-09</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.002640987746417522</v>
+        <v>1.73413838844283e-10</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.0003359327092766762</v>
+        <v>2.207501959006208e-10</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.00160018471069634</v>
+        <v>6.534238705668827e-10</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.002501601818948984</v>
+        <v>7.713071292769769e-10</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.003325775265693665</v>
+        <v>2.338535962098653e-11</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.002699533477425575</v>
+        <v>8.208991819635969e-11</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.0004655827069655061</v>
+        <v>1.965868301478935e-10</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.002943424042314291</v>
+        <v>3.478127508227402e-11</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.0002089129702653736</v>
+        <v>1.562984464076322e-11</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.002044148975983262</v>
+        <v>8.243634108673348e-10</v>
       </c>
       <c r="DS5" t="n">
-        <v>4.884004010818899e-05</v>
+        <v>5.316895812512712e-10</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.0001882006181403995</v>
+        <v>3.678174431698267e-10</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.000787976779974997</v>
+        <v>2.205080285033745e-10</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.0004515318432822824</v>
+        <v>4.375044215798596e-10</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.0007109590223990381</v>
+        <v>2.007333362030739e-11</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.004710923414677382</v>
+        <v>7.975553550920722e-10</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.55226647015661e-05</v>
+        <v>4.331118519385058e-10</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.001038722926750779</v>
+        <v>9.119514032818188e-10</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.001244784914888442</v>
+        <v>7.289740477922635e-10</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.0007954634493216872</v>
+        <v>4.857231838961695e-10</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0005016406648792326</v>
+        <v>4.244968543343219e-10</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.001335760578513145</v>
+        <v>2.724001857412617e-10</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.0005660514580085874</v>
+        <v>5.99590155303531e-10</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.0005502133863046765</v>
+        <v>3.96540605906992e-10</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.002582389395684004</v>
+        <v>7.1323474903906e-10</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.001083613373339176</v>
+        <v>1.475225080982412e-10</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.0003106893564108759</v>
+        <v>4.273069745264202e-11</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.000174344313563779</v>
+        <v>5.887569598517217e-11</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.0008049834286794066</v>
+        <v>2.92921409350555e-10</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.002661891747266054</v>
+        <v>9.547855561731211e-11</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.0004732591041829437</v>
+        <v>1.723091808125687e-10</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.0002282487548654899</v>
+        <v>6.585316320029122e-11</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.001937626861035824</v>
+        <v>3.263085079918682e-10</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.001188547350466251</v>
+        <v>3.632046885471141e-10</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.002195402048528194</v>
+        <v>7.412109120918942e-11</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.000499500660225749</v>
+        <v>2.865052084466413e-10</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.001036139554344118</v>
+        <v>2.525267772668371e-10</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.001736427424475551</v>
+        <v>3.538375703548979e-10</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.00101258757058531</v>
+        <v>4.476525816698995e-10</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.002279114676639438</v>
+        <v>2.538898535853207e-10</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.0001219537225551903</v>
+        <v>1.604828422929749e-11</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.001330162049271166</v>
+        <v>1.918426528746409e-10</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.003854110604152083</v>
+        <v>1.819299849659117e-10</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.0009832474170252681</v>
+        <v>1.693937767832665e-10</v>
       </c>
       <c r="FA5" t="n">
-        <v>7.380402166745625e-06</v>
+        <v>1.6017846771188e-10</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.001206501969136298</v>
+        <v>1.077198191756779e-10</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.0001934258616529405</v>
+        <v>7.803549473273108e-11</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.001564163714647293</v>
+        <v>4.315491367035129e-11</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.0008338944753631949</v>
+        <v>2.678042163029026e-11</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.001494834665209055</v>
+        <v>1.068299337880774e-10</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.0007364077027887106</v>
+        <v>4.225375882516147e-10</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.0006753172492608428</v>
+        <v>6.40667019435881e-10</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.002321754349395633</v>
+        <v>1.732781279573103e-10</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.001174047589302063</v>
+        <v>2.944664997950319e-11</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.001337873400188982</v>
+        <v>2.833175083427619e-10</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.003041877876967192</v>
+        <v>1.651643266598057e-10</v>
       </c>
       <c r="FM5" t="n">
-        <v>8.446758147329092e-05</v>
+        <v>1.418743317271876e-10</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.002570474753156304</v>
+        <v>6.750665582089255e-10</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.002884719055145979</v>
+        <v>9.796556899033249e-10</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.002491197548806667</v>
+        <v>2.907277474317738e-10</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.003353813663125038</v>
+        <v>1.522261539044223e-09</v>
       </c>
       <c r="FR5" t="n">
-        <v>4.180939868092537e-05</v>
+        <v>3.335193232700817e-12</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.002316394820809364</v>
+        <v>7.726086992398962e-10</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.00454313587397337</v>
+        <v>9.976840464887005e-10</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.00270769651979208</v>
+        <v>6.04735428400005e-10</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.0002575370599515736</v>
+        <v>9.418511526249063e-10</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.002765243640169501</v>
+        <v>1.563607687771196e-09</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.001743326080031693</v>
+        <v>3.412494176124881e-10</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.003949509467929602</v>
+        <v>9.976057480098888e-11</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.0007977845380082726</v>
+        <v>2.116842534594099e-10</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.001137515646405518</v>
+        <v>6.509380812147469e-10</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.0009009112836793065</v>
+        <v>6.087329529336216e-10</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.0003296680515632033</v>
+        <v>6.798861473811257e-10</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.003146566916257143</v>
+        <v>4.038881451506882e-10</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.003226920263841748</v>
+        <v>2.210183425166434e-10</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.002489946084097028</v>
+        <v>4.834000821157813e-12</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.001140151056461036</v>
+        <v>1.806766264378368e-10</v>
       </c>
     </row>
     <row r="6">
@@ -3844,1140 +3844,1140 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.01749461516737938</v>
+        <v>0.04963399842381477</v>
       </c>
       <c r="B7" t="n">
-        <v>0.336054652929306</v>
+        <v>0.2704120278358459</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001769015216268599</v>
+        <v>0.1517814099788666</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2101438045501709</v>
+        <v>0.1639127433300018</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03896214812994003</v>
+        <v>0.0699378028512001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02554092742502689</v>
+        <v>0.07855643332004547</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02305513992905617</v>
+        <v>0.1660260856151581</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05281304195523262</v>
+        <v>0.1165159791707993</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04238639771938324</v>
+        <v>0.1127550229430199</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02129192464053631</v>
+        <v>0.06532192230224609</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2784970998764038</v>
+        <v>0.341813713312149</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01753385178744793</v>
+        <v>0.1562181860208511</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1849109679460526</v>
+        <v>0.2174760848283768</v>
       </c>
       <c r="N7" t="n">
-        <v>0.07705268263816833</v>
+        <v>0.08813122659921646</v>
       </c>
       <c r="O7" t="n">
-        <v>0.07808135449886322</v>
+        <v>0.01948968507349491</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01174179650843143</v>
+        <v>0.07504642009735107</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.02438727021217346</v>
+        <v>0.2194747179746628</v>
       </c>
       <c r="R7" t="n">
-        <v>0.02983515337109566</v>
+        <v>0.08656094968318939</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01477943826466799</v>
+        <v>0.02107858657836914</v>
       </c>
       <c r="T7" t="n">
-        <v>0.02883975207805634</v>
+        <v>0.05878715217113495</v>
       </c>
       <c r="U7" t="n">
-        <v>0.003054209984838963</v>
+        <v>0.07999958097934723</v>
       </c>
       <c r="V7" t="n">
-        <v>0.02048361115157604</v>
+        <v>0.01644772291183472</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01718337461352348</v>
+        <v>0.01212167181074619</v>
       </c>
       <c r="X7" t="n">
-        <v>0.02431385405361652</v>
+        <v>0.09895143657922745</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.02913597412407398</v>
+        <v>0.008940914645791054</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.04894454032182693</v>
+        <v>0.03838036209344864</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.04212301224470139</v>
+        <v>0.103455439209938</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.03864895179867744</v>
+        <v>0.04843819513916969</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.03346508741378784</v>
+        <v>0.001445182831957936</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.01922417059540749</v>
+        <v>0.03343698382377625</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.02045218087732792</v>
+        <v>0.2288738787174225</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0307279285043478</v>
+        <v>0.05865325033664703</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.02881253510713577</v>
+        <v>0.1808177679777145</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.007512318901717663</v>
+        <v>0.07549018412828445</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.01918620243668556</v>
+        <v>0.008078719489276409</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.001890676096081734</v>
+        <v>0.0005576205439865589</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.006732242181897163</v>
+        <v>0.009606875479221344</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.01449014432728291</v>
+        <v>0.1756860911846161</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.00684451637789607</v>
+        <v>0.05841274932026863</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.01295268815010786</v>
+        <v>0.03292021900415421</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.02584080584347248</v>
+        <v>0.08883395791053772</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.01840069517493248</v>
+        <v>0.006766157224774361</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.015384241938591</v>
+        <v>0.00636720284819603</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.005467143841087818</v>
+        <v>0.05161099508404732</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.004915316589176655</v>
+        <v>0.01108561083674431</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.04685200378298759</v>
+        <v>0.003244956955313683</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.209482342004776</v>
+        <v>0.2266937047243118</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.03633763268589973</v>
+        <v>0.03263840079307556</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.04978913441300392</v>
+        <v>0.1024863868951797</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.01349901873618364</v>
+        <v>0.108566552400589</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.008104206994175911</v>
+        <v>0.07193168252706528</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.005966387689113617</v>
+        <v>0.0009928587824106216</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.03800850734114647</v>
+        <v>0.08432699739933014</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.01853165030479431</v>
+        <v>0.009469333104789257</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.01076901145279408</v>
+        <v>0.0206466019153595</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.06935596466064453</v>
+        <v>0.1472204029560089</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.08028792589902878</v>
+        <v>0.1176238059997559</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.06423627585172653</v>
+        <v>0.1032739505171776</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.1009151339530945</v>
+        <v>0.105553150177002</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.006170173641294241</v>
+        <v>0.1222266107797623</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.00725330738350749</v>
+        <v>0.03857547044754028</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.04384276270866394</v>
+        <v>0.09676866233348846</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.02429556846618652</v>
+        <v>0.1695570647716522</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.03823095932602882</v>
+        <v>0.008185620419681072</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.02209564857184887</v>
+        <v>0.06915093958377838</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.01194832846522331</v>
+        <v>0.00614503026008606</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.01352412905544043</v>
+        <v>0.06010264530777931</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.02650200203061104</v>
+        <v>0.05883597210049629</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.03930170461535454</v>
+        <v>0.03345245867967606</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.006044872105121613</v>
+        <v>0.03006901405751705</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.02320835366845131</v>
+        <v>0.04095689952373505</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.004851298406720161</v>
+        <v>0.0134249497205019</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.03286215290427208</v>
+        <v>0.03120824508368969</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.09842094779014587</v>
+        <v>0.1956728398799896</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.001491874339990318</v>
+        <v>0.0242774598300457</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.02880774438381195</v>
+        <v>0.04225537553429604</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.03218982368707657</v>
+        <v>0.04612534493207932</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.0122867077589035</v>
+        <v>0.07304788380861282</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.02203447930514812</v>
+        <v>0.007851935923099518</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.00256432918831706</v>
+        <v>0.1220665797591209</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.03281259164214134</v>
+        <v>0.08199777454137802</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.009892720729112625</v>
+        <v>0.01696336269378662</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.04955167323350906</v>
+        <v>0.09595479816198349</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.02274714037775993</v>
+        <v>0.03918693214654922</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.02754395268857479</v>
+        <v>0.06929980963468552</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.01544403191655874</v>
+        <v>0.007653553038835526</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.01028331089764833</v>
+        <v>0.00334245478734374</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.009837527759373188</v>
+        <v>0.02162717841565609</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0001980667002499104</v>
+        <v>0.02174101024866104</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.02166465669870377</v>
+        <v>0.01560054905712605</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.05039254948496819</v>
+        <v>0.08113855123519897</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.003563764039427042</v>
+        <v>0.04778560623526573</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.009904524311423302</v>
+        <v>0.001731237396597862</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.03766901791095734</v>
+        <v>0.210218608379364</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.01277881860733032</v>
+        <v>0.1335300505161285</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.03507706895470619</v>
+        <v>0.07088139653205872</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.05354601517319679</v>
+        <v>0.06957869976758957</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.0450713150203228</v>
+        <v>0.03683197498321533</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.008422376587986946</v>
+        <v>0.09353327006101608</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.005400598049163818</v>
+        <v>0.01309519074857235</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.04314865544438362</v>
+        <v>0.09765402972698212</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.03233780339360237</v>
+        <v>0.03762437403202057</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.03676283359527588</v>
+        <v>0.07908221334218979</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.01691687852144241</v>
+        <v>0.00490905437618494</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.01104033645242453</v>
+        <v>0.007863965816795826</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.0134571734815836</v>
+        <v>0.02023892104625702</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.01201780140399933</v>
+        <v>0.02567124180495739</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.01434910483658314</v>
+        <v>0.02551164291799068</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.006203217897564173</v>
+        <v>0.01127181015908718</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.02670623362064362</v>
+        <v>0.06568542867898941</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.03032246604561806</v>
+        <v>0.1326564848423004</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.08414817601442337</v>
+        <v>0.03315984830260277</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.05077948793768883</v>
+        <v>0.03962645679712296</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.004168327897787094</v>
+        <v>0.2194844633340836</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.02947595715522766</v>
+        <v>0.05489742755889893</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.02875505201518536</v>
+        <v>0.152315616607666</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.03087193332612514</v>
+        <v>0.01526508666574955</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.0138591593131423</v>
+        <v>0.01617751270532608</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.003230943810194731</v>
+        <v>0.02361046150326729</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.01301401481032372</v>
+        <v>0.01199738774448633</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.003320136340335011</v>
+        <v>0.04499528929591179</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.02341177873313427</v>
+        <v>0.0125480042770505</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.04343638196587563</v>
+        <v>0.001760405022650957</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.00318798515945673</v>
+        <v>0.02176411636173725</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.03078148514032364</v>
+        <v>0.01910658925771713</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.02821123413741589</v>
+        <v>0.1697100698947906</v>
       </c>
       <c r="DW7" t="n">
-        <v>3.240769729018211e-05</v>
+        <v>0.004344098269939423</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.003746781498193741</v>
+        <v>0.03732862323522568</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.03797295689582825</v>
+        <v>0.0571746826171875</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.03318977355957031</v>
+        <v>0.02480817772448063</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.01588424295186996</v>
+        <v>0.03643465042114258</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.01001348905265331</v>
+        <v>0.09179748594760895</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.0146589819341898</v>
+        <v>0.02331123128533363</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.008566716685891151</v>
+        <v>0.08139805495738983</v>
       </c>
       <c r="EE7" t="n">
-        <v>9.061023592948914e-05</v>
+        <v>0.07653114944696426</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.01555509213358164</v>
+        <v>0.02180729061365128</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.04944857209920883</v>
+        <v>0.0603276714682579</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.03623170405626297</v>
+        <v>0.03028175979852676</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.004921993240714073</v>
+        <v>0.06349661201238632</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.01764643937349319</v>
+        <v>0.0002872326876968145</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.01948077231645584</v>
+        <v>0.05013290047645569</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.01144460588693619</v>
+        <v>0.001052644103765488</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.004030149430036545</v>
+        <v>0.01282611675560474</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.01989035308361053</v>
+        <v>0.01478967349976301</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.004179383628070354</v>
+        <v>0.02929070219397545</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.02266180701553822</v>
+        <v>0.08094994723796844</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.04103059321641922</v>
+        <v>0.0273125059902668</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.006662069819867611</v>
+        <v>0.02522078156471252</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.01520288549363613</v>
+        <v>0.07254455983638763</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.0365947037935257</v>
+        <v>0.0196511410176754</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.03496914729475975</v>
+        <v>0.05844665318727493</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.03653731197118759</v>
+        <v>0.01940172165632248</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.005835366435348988</v>
+        <v>0.08246060460805893</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.0002078512916341424</v>
+        <v>0.01508981734514236</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.04638001322746277</v>
+        <v>0.1090978980064392</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.0190617460757494</v>
+        <v>0.02393916063010693</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.02849311381578445</v>
+        <v>0.07434485852718353</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.01810207217931747</v>
+        <v>0.006985258311033249</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.01310627534985542</v>
+        <v>0.0181454848498106</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.01670447736978531</v>
+        <v>0.01754314824938774</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.007689914666116238</v>
+        <v>0.02415714599192142</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.02371981926262379</v>
+        <v>0.02232659421861172</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.000571542652323842</v>
+        <v>0.01025693956762552</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.03495955839753151</v>
+        <v>0.05834362283349037</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.02655265852808952</v>
+        <v>0.06166971102356911</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.03369306772947311</v>
+        <v>0.061433345079422</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.01341901905834675</v>
+        <v>0.07692635059356689</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.02039993554353714</v>
+        <v>0.03330820053815842</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.003740128595381975</v>
+        <v>0.01093381084501743</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.002936520148068666</v>
+        <v>0.01348960306495428</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.01318507269024849</v>
+        <v>0.1367361843585968</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.004478650167584419</v>
+        <v>0.02782261744141579</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.06927105039358139</v>
+        <v>0.1163965314626694</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.04570295289158821</v>
+        <v>0.01765888184309006</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.01875703036785126</v>
+        <v>0.04328877478837967</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.005849087610840797</v>
+        <v>0.0974975973367691</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.01308904774487019</v>
+        <v>0.0009423983283340931</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.01180094480514526</v>
+        <v>0.07361118495464325</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.007030779495835304</v>
+        <v>0.04321921989321709</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.02901250496506691</v>
+        <v>0.0863645076751709</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.0453663244843483</v>
+        <v>0.02707336470484734</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.02597565203905106</v>
+        <v>0.1363100409507751</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.01798609830439091</v>
+        <v>0.06961189210414886</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.006632606498897076</v>
+        <v>0.009987980127334595</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.005244524218142033</v>
+        <v>0.0267229937016964</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.06502917408943176</v>
+        <v>0.01341763511300087</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.1013016104698181</v>
+        <v>0.1119124069809914</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.02950155921280384</v>
+        <v>0.02603031694889069</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.02945847623050213</v>
+        <v>0.003199646016582847</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.02054424956440926</v>
+        <v>0.1515325754880905</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1541447788476944</v>
+        <v>0.8841161727905273</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01171651110053062</v>
+        <v>0.05362778902053833</v>
       </c>
       <c r="D8" t="n">
-        <v>0.08173266798257828</v>
+        <v>0.1091771721839905</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02274532802402973</v>
+        <v>0.2340045869350433</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1011764779686928</v>
+        <v>0.6180094480514526</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004441476427018642</v>
+        <v>0.02336873114109039</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03371528536081314</v>
+        <v>0.1033459305763245</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003980409353971481</v>
+        <v>0.20211261510849</v>
       </c>
       <c r="J8" t="n">
-        <v>0.04520372301340103</v>
+        <v>0.04184778034687042</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1179286241531372</v>
+        <v>1.160749435424805</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00294628064148128</v>
+        <v>0.08719362318515778</v>
       </c>
       <c r="M8" t="n">
-        <v>0.07365146279335022</v>
+        <v>0.2650033831596375</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02176201902329922</v>
+        <v>0.08738884329795837</v>
       </c>
       <c r="O8" t="n">
-        <v>0.107567697763443</v>
+        <v>0.6579214334487915</v>
       </c>
       <c r="P8" t="n">
-        <v>0.004576352424919605</v>
+        <v>0.1271239072084427</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.008872402831912041</v>
+        <v>0.1723767668008804</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0003022318123839796</v>
+        <v>0.1189370974898338</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01064970158040524</v>
+        <v>0.09523191303014755</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02084491401910782</v>
+        <v>0.2566047310829163</v>
       </c>
       <c r="U8" t="n">
-        <v>0.008988916873931885</v>
+        <v>0.05040357634425163</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0124060120433569</v>
+        <v>0.2168690115213394</v>
       </c>
       <c r="W8" t="n">
-        <v>0.007449802942574024</v>
+        <v>0.1059992909431458</v>
       </c>
       <c r="X8" t="n">
-        <v>0.009126972407102585</v>
+        <v>0.05441303551197052</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01893297396600246</v>
+        <v>0.09325800091028214</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01181428320705891</v>
+        <v>0.2983829379081726</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01692814566195011</v>
+        <v>0.03697257488965988</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0007570534944534302</v>
+        <v>0.1159076541662216</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.01722178608179092</v>
+        <v>0.1007362455129623</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.005222648847848177</v>
+        <v>0.09675118327140808</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0006213702727109194</v>
+        <v>0.2156289368867874</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.01059006061404943</v>
+        <v>0.5188249945640564</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.005721245426684618</v>
+        <v>0.1924318671226501</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.01056879013776779</v>
+        <v>0.01693896949291229</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.00875382125377655</v>
+        <v>0.3237586617469788</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.003110786667093635</v>
+        <v>0.0356425829231739</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.01287087798118591</v>
+        <v>0.03575938940048218</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.02255245484411716</v>
+        <v>0.2681728899478912</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.007919392548501492</v>
+        <v>0.04489455744624138</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.005070779006928205</v>
+        <v>0.1071348860859871</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.007548168301582336</v>
+        <v>0.1441574394702911</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.02004710771143436</v>
+        <v>0.165186271071434</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.00450096232816577</v>
+        <v>0.1600938439369202</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.006954257842153311</v>
+        <v>0.3786165118217468</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.0225945021957159</v>
+        <v>0.1076610535383224</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.01217802427709103</v>
+        <v>0.08011889457702637</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.09714170545339584</v>
+        <v>1.138657331466675</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.008235120214521885</v>
+        <v>0.009923756122589111</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.0003693974576890469</v>
+        <v>0.006742121651768684</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.001146107912063599</v>
+        <v>0.01980607211589813</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.05795254930853844</v>
+        <v>0.5451326370239258</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.003100724890828133</v>
+        <v>0.02324843779206276</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.03103127330541611</v>
+        <v>0.005783244967460632</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.03511251509189606</v>
+        <v>0.05557333305478096</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.02488536201417446</v>
+        <v>0.006488822400569916</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.02926093712449074</v>
+        <v>0.1437322795391083</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.04085434973239899</v>
+        <v>0.02668417990207672</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.02448496408760548</v>
+        <v>0.184607982635498</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.04558576643466949</v>
+        <v>0.2736319005489349</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.02771538123488426</v>
+        <v>0.07549818605184555</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.01171983126550913</v>
+        <v>0.1150953024625778</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.03624960035085678</v>
+        <v>0.001434233039617538</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.003005619626492262</v>
+        <v>0.09651245921850204</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.002553754951804876</v>
+        <v>0.1468755006790161</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.02155166864395142</v>
+        <v>0.08397487550973892</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.01888877712190151</v>
+        <v>0.005297522060573101</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.01978622190654278</v>
+        <v>0.1119455695152283</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.001231378642842174</v>
+        <v>0.07537408173084259</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.0003131866687908769</v>
+        <v>0.05811654031276703</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.02117399871349335</v>
+        <v>0.1282213926315308</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.005326866637915373</v>
+        <v>0.01791641488671303</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.001886234618723392</v>
+        <v>0.119278572499752</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.007947856560349464</v>
+        <v>0.129519060254097</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.04924914240837097</v>
+        <v>0.7341715693473816</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.02337438613176346</v>
+        <v>0.02897646836936474</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.01369111798703671</v>
+        <v>0.1495527923107147</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.01323506236076355</v>
+        <v>0.08722188323736191</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.01811324059963226</v>
+        <v>0.3036389350891113</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.01410525012761354</v>
+        <v>0.1080312132835388</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.01538914628326893</v>
+        <v>0.1436223536729813</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.02485889755189419</v>
+        <v>0.03461679443717003</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.0009709198493510485</v>
+        <v>0.05079217255115509</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.02539891004562378</v>
+        <v>0.28790482878685</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.01993360556662083</v>
+        <v>0.01506044901907444</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.01487281825393438</v>
+        <v>0.05672118440270424</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.01049923337996006</v>
+        <v>0.05580127239227295</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.01751353219151497</v>
+        <v>0.1966173350811005</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.009773348458111286</v>
+        <v>0.08963264524936676</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.004854809958487749</v>
+        <v>0.01494626421481371</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.01401029247790575</v>
+        <v>0.03119836375117302</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.01938649266958237</v>
+        <v>0.1848575323820114</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.003352775005623698</v>
+        <v>0.620587170124054</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.009701211005449295</v>
+        <v>0.01263787783682346</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.02308746427297592</v>
+        <v>0.2947666645050049</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.00529091153293848</v>
+        <v>0.1896461546421051</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.001781660597771406</v>
+        <v>0.3348738849163055</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.01939998939633369</v>
+        <v>0.09525592625141144</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.01682831533253193</v>
+        <v>0.01657510548830032</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.0004072985611855984</v>
+        <v>0.1104570925235748</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.001347206067293882</v>
+        <v>0.006065532565116882</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.02299322560429573</v>
+        <v>0.2720421254634857</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.01918674074113369</v>
+        <v>0.0107357781380415</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.02192344516515732</v>
+        <v>0.06546323746442795</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.01029690448194742</v>
+        <v>0.07294817268848419</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.01885723136365414</v>
+        <v>0.1912532150745392</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.009340828284621239</v>
+        <v>0.03299601748585701</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.01399167440831661</v>
+        <v>0.02609094232320786</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.01010886393487453</v>
+        <v>0.05316882580518723</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.00532482797279954</v>
+        <v>0.02710859104990959</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.0269454475492239</v>
+        <v>0.1248908936977386</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.005423343740403652</v>
+        <v>0.03255750611424446</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.0548427551984787</v>
+        <v>0.0131901241838932</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.006971968337893486</v>
+        <v>0.4298876821994781</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.01526784803718328</v>
+        <v>0.1663652062416077</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.0249808244407177</v>
+        <v>0.1894417703151703</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.02585091814398766</v>
+        <v>0.09025415778160095</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.01150512509047985</v>
+        <v>0.1504806727170944</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.0004446341190487146</v>
+        <v>0.01075219735503197</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.004876273218542337</v>
+        <v>0.1563525795936584</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.01316289603710175</v>
+        <v>0.02362531796097755</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.0120595209300518</v>
+        <v>0.2101630717515945</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.00674870703369379</v>
+        <v>0.06991726160049438</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.0007534219184890389</v>
+        <v>0.06940396130084991</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.002406643703579903</v>
+        <v>0.04449290037155151</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.0003575221635401249</v>
+        <v>0.2551029622554779</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.02030427940189838</v>
+        <v>0.008099574595689774</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.004735038615763187</v>
+        <v>0.1279754936695099</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.01115542370826006</v>
+        <v>0.04355880618095398</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.02352325059473515</v>
+        <v>0.005815565586090088</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.00213361531496048</v>
+        <v>0.02849375270307064</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.006478271447122097</v>
+        <v>0.1002845615148544</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.01184908859431744</v>
+        <v>0.1517615616321564</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.0005185280460864305</v>
+        <v>0.01466242223978043</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.006821702234447002</v>
+        <v>0.06024618819355965</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.004231369122862816</v>
+        <v>0.2316708415746689</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.009791303426027298</v>
+        <v>0.02568943053483963</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.01699800975620747</v>
+        <v>0.0738433301448822</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.0141812851652503</v>
+        <v>0.05624538660049438</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.00126372289378196</v>
+        <v>0.03633784875273705</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.003749635070562363</v>
+        <v>0.1672899127006531</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.01120447739958763</v>
+        <v>0.02657009661197662</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.01757904887199402</v>
+        <v>0.06778977066278458</v>
       </c>
       <c r="EM8" t="n">
-        <v>6.19812635704875e-05</v>
+        <v>0.06404776126146317</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.003460365813225508</v>
+        <v>0.04621332511305809</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.004188934341073036</v>
+        <v>0.01027093827724457</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.009938753210008144</v>
+        <v>0.1086999550461769</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.02181875146925449</v>
+        <v>0.01529372110962868</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.01467712596058846</v>
+        <v>0.1096427589654922</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.01804769411683083</v>
+        <v>0.215316578745842</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.01974540762603283</v>
+        <v>0.06047892197966576</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.02113049104809761</v>
+        <v>0.07370661199092865</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.02497133798897266</v>
+        <v>0.01157866045832634</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.0007540013175457716</v>
+        <v>0.04748912155628204</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.002260385081171989</v>
+        <v>0.0501357726752758</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.02174869924783707</v>
+        <v>0.3105911016464233</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.01511343102902174</v>
+        <v>0.01242291741073132</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.01713182404637337</v>
+        <v>0.05871445685625076</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.01212081965059042</v>
+        <v>0.1246891021728516</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.01517320889979601</v>
+        <v>0.1886798143386841</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.01594740897417068</v>
+        <v>0.1062600910663605</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.008360372856259346</v>
+        <v>0.03746769577264786</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.01631826907396317</v>
+        <v>0.07097014784812927</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.002573833102360368</v>
+        <v>0.03981824219226837</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.01144919916987419</v>
+        <v>0.2941834032535553</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.01957546547055244</v>
+        <v>0.01407252252101898</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.02402395755052567</v>
+        <v>0.2448942363262177</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.007941323332488537</v>
+        <v>0.09759210050106049</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.01246618945151567</v>
+        <v>0.2265338599681854</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.007343288511037827</v>
+        <v>0.1579291373491287</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.005570081528276205</v>
+        <v>0.3102906048297882</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.01177260931581259</v>
+        <v>0.02306731417775154</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.007160510867834091</v>
+        <v>0.04745469614863396</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.02461561188101768</v>
+        <v>0.3743967711925507</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.01329601183533669</v>
+        <v>0.04494528472423553</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.02610146254301071</v>
+        <v>0.3335327506065369</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.02313297241926193</v>
+        <v>0.04651948809623718</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.0139641035348177</v>
+        <v>0.06514313071966171</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.01349238120019436</v>
+        <v>0.1286828219890594</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.01043792255222797</v>
+        <v>0.1322223246097565</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.003558184253051877</v>
+        <v>0.081299789249897</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.02979935519397259</v>
+        <v>0.1736568510532379</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.0005325478268787265</v>
+        <v>0.135596975684166</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.003506271168589592</v>
+        <v>0.01782628521323204</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.002943465951830149</v>
+        <v>0.09748828411102295</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.007713175378739834</v>
+        <v>0.09164547920227051</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.01596568524837494</v>
+        <v>0.01204665750265121</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.07000645995140076</v>
+        <v>0.09263619035482407</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.004848400130867958</v>
+        <v>0.1099108457565308</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.009129069745540619</v>
+        <v>0.1592724621295929</v>
       </c>
     </row>
     <row r="9">
@@ -5551,2278 +5551,2278 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.2805963456630707</v>
+        <v>0.0001361511531285942</v>
       </c>
       <c r="B10" t="n">
-        <v>0.441979855298996</v>
+        <v>0.003801244543865323</v>
       </c>
       <c r="C10" t="n">
-        <v>0.06113296002149582</v>
+        <v>0.0007711796788498759</v>
       </c>
       <c r="D10" t="n">
-        <v>0.05982346460223198</v>
+        <v>0.0002530019264668226</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6831540465354919</v>
+        <v>0.0007424868526868522</v>
       </c>
       <c r="F10" t="n">
-        <v>0.07045173645019531</v>
+        <v>0.001308220322243869</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04902379214763641</v>
+        <v>0.0006812518695369363</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2069366574287415</v>
+        <v>0.0009013294475153089</v>
       </c>
       <c r="I10" t="n">
-        <v>0.03974799066781998</v>
+        <v>0.000312127114739269</v>
       </c>
       <c r="J10" t="n">
-        <v>0.02292834222316742</v>
+        <v>0.00147634232416749</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3392647206783295</v>
+        <v>0.004211048129945993</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02494445443153381</v>
+        <v>0.001322243944741786</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01493038237094879</v>
+        <v>0.001689873170107603</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5555555820465088</v>
+        <v>0.002321199979633093</v>
       </c>
       <c r="O10" t="n">
-        <v>0.03318819403648376</v>
+        <v>0.001437304192222655</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01484200358390808</v>
+        <v>0.001935625681653619</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4409193992614746</v>
+        <v>0.002733784029260278</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1815718561410904</v>
+        <v>9.527837391942739e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1205582469701767</v>
+        <v>0.001107233576476574</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1664027273654938</v>
+        <v>0.002369800582528114</v>
       </c>
       <c r="U10" t="n">
-        <v>0.009848351590335369</v>
+        <v>0.0006854630773887038</v>
       </c>
       <c r="V10" t="n">
-        <v>0.05168601498007774</v>
+        <v>0.0006091990508139133</v>
       </c>
       <c r="W10" t="n">
-        <v>0.04122939333319664</v>
+        <v>0.0009533071424812078</v>
       </c>
       <c r="X10" t="n">
-        <v>0.06173713877797127</v>
+        <v>0.0002839916269294918</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0804702490568161</v>
+        <v>0.0001561378012411296</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.02902509272098541</v>
+        <v>0.0005052607739344239</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.02057936415076256</v>
+        <v>0.0007993570761755109</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0762329176068306</v>
+        <v>0.0006789203616790473</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.144304022192955</v>
+        <v>0.001243336242623627</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.04054269939661026</v>
+        <v>0.0003742802946362644</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.01358820497989655</v>
+        <v>0.0012969677336514</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.2100554406642914</v>
+        <v>0.002722723642364144</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.07199429720640182</v>
+        <v>0.0002362332888878882</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.1974164545536041</v>
+        <v>0.000461059098597616</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.1209036409854889</v>
+        <v>0.0007461467175744474</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.02816823869943619</v>
+        <v>0.0002423096302663907</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.2574462592601776</v>
+        <v>0.001270723296329379</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.02497842721641064</v>
+        <v>0.002159300958737731</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.03198706731200218</v>
+        <v>0.0002831790188793093</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.02622867934405804</v>
+        <v>0.0002905621659010649</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.1381444185972214</v>
+        <v>0.0005360125796869397</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.04627789184451103</v>
+        <v>0.0001105622504837811</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.09830465167760849</v>
+        <v>0.0002903217682614923</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.05009977146983147</v>
+        <v>0.0002427660510875285</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.02783438749611378</v>
+        <v>0.0003052655956707895</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.1171659901738167</v>
+        <v>0.001963502261787653</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.8384698629379272</v>
+        <v>0.004655820783227682</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.09629818052053452</v>
+        <v>0.0008337070466950536</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.2447023540735245</v>
+        <v>0.001116766477935016</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.04101774841547012</v>
+        <v>0.0003527067601680756</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.0920974463224411</v>
+        <v>0.0004010976990684867</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.05787979438900948</v>
+        <v>2.504508302081376e-05</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.189133957028389</v>
+        <v>0.0003481286694295704</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.06557884812355042</v>
+        <v>0.0003843760350719094</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.1150642856955528</v>
+        <v>0.002010217402130365</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.07427400350570679</v>
+        <v>0.0006379688275046647</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.1193651705980301</v>
+        <v>0.0001221649872604758</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.1531386226415634</v>
+        <v>0.0006034611142240465</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.2889701128005981</v>
+        <v>0.002978181233629584</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.0498034805059433</v>
+        <v>2.53668986260891e-05</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.1313077509403229</v>
+        <v>0.0008547886973246932</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.2180470079183578</v>
+        <v>0.0003612426808103919</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.03995509818196297</v>
+        <v>0.001144063659012318</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.1007704064249992</v>
+        <v>0.0002857481013052166</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.6551312804222107</v>
+        <v>0.0001411022385582328</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.05229272693395615</v>
+        <v>3.689224104164168e-05</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.3572554886341095</v>
+        <v>0.0001697517582215369</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.5692450404167175</v>
+        <v>0.001543912338092923</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.1472991555929184</v>
+        <v>0.001175790326669812</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.05150902271270752</v>
+        <v>0.0005447751027531922</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.2590013444423676</v>
+        <v>0.0001557770883664489</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.007992099970579147</v>
+        <v>0.0003078056033700705</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.06196014583110809</v>
+        <v>0.002674434566870332</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.4483594596385956</v>
+        <v>0.004052591510117054</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.1600461453199387</v>
+        <v>0.0007092911982908845</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.02503859251737595</v>
+        <v>0.0008525758748874068</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.03613701835274696</v>
+        <v>0.0007041125209070742</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.1675861924886703</v>
+        <v>0.0006688912399113178</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.2559755742549896</v>
+        <v>2.613811375340447e-05</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.1069889143109322</v>
+        <v>0.0007007834501564503</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.03464905545115471</v>
+        <v>7.979430665727705e-05</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.01177250221371651</v>
+        <v>0.000283502449747175</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.08019564300775528</v>
+        <v>0.0009579900652170181</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.009767176583409309</v>
+        <v>0.0002442084369249642</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.04478758201003075</v>
+        <v>5.685680662281811e-05</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.07109620422124863</v>
+        <v>0.0003682963433675468</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.07605051249265671</v>
+        <v>0.0007028768304735422</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.0100842509418726</v>
+        <v>3.027938510058448e-05</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.05932116508483887</v>
+        <v>0.0002684828359633684</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.03817098215222359</v>
+        <v>0.0003020558797288686</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.4008621573448181</v>
+        <v>0.001188203925266862</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.5748123526573181</v>
+        <v>0.002256862353533506</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.02514824643731117</v>
+        <v>0.0007074574823491275</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.1414861232042313</v>
+        <v>0.001310475519858301</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.4946461319923401</v>
+        <v>0.00265696132555604</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.02660372667014599</v>
+        <v>0.0003608912229537964</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.1083959564566612</v>
+        <v>0.0007187275332398713</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.1664955615997314</v>
+        <v>0.000510817626491189</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.0294182151556015</v>
+        <v>0.000449696701252833</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.02080424502491951</v>
+        <v>7.881858618929982e-05</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.02967895939946175</v>
+        <v>0.0008439362281933427</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.01389896869659424</v>
+        <v>0.0002722630160860717</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.09214332699775696</v>
+        <v>4.841556074097753e-05</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.06693867594003677</v>
+        <v>0.0003106871736235917</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.07870714366436005</v>
+        <v>0.0005803706590086222</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.005708150565624237</v>
+        <v>0.0002571498916950077</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.0135590573772788</v>
+        <v>0.0005624584737233818</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.02151814661920071</v>
+        <v>0.00024256925098598</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.4687318205833435</v>
+        <v>0.0003783248830586672</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.3455424606800079</v>
+        <v>0.001392493373714387</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.04790622368454933</v>
+        <v>7.448767428286374e-05</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.4928714036941528</v>
+        <v>0.0009282692335546017</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.1293278783559799</v>
+        <v>0.0002591312804725021</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.04848993942141533</v>
+        <v>0.0009354015346616507</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.5217032432556152</v>
+        <v>0.0004832265258301049</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.107688844203949</v>
+        <v>0.0006407022010535002</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.006685155443847179</v>
+        <v>0.002751867286860943</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.2248201668262482</v>
+        <v>0.0006769403116777539</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.2072355896234512</v>
+        <v>0.001051167608238757</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.02217424474656582</v>
+        <v>0.0001441013009753078</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.172416165471077</v>
+        <v>8.806513505987823e-05</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.02693499252200127</v>
+        <v>0.0001940004585776478</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.05426689237356186</v>
+        <v>0.00132636004127562</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.0595284178853035</v>
+        <v>0.0002609126968309283</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.1840282082557678</v>
+        <v>0.0006110331742092967</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.004335145931690931</v>
+        <v>1.423293724656105e-05</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.1076685637235641</v>
+        <v>0.000403835583711043</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.1818699240684509</v>
+        <v>0.0006363102002069354</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.01435653492808342</v>
+        <v>0.0002643590560182929</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.2409279048442841</v>
+        <v>0.000274082034593448</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.002075866796076298</v>
+        <v>0.0019036247394979</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.06400629132986069</v>
+        <v>0.0006725569255650043</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.1742912530899048</v>
+        <v>1.810665708035231e-05</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.02352697029709816</v>
+        <v>0.001180382678285241</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.01897202059626579</v>
+        <v>0.0002552953083068132</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.07470757514238358</v>
+        <v>0.0004353563999757171</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.04160713404417038</v>
+        <v>1.584368874318898e-05</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.02490838058292866</v>
+        <v>0.0004211809718981385</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.2548883259296417</v>
+        <v>0.0006371784256771207</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.1279296576976776</v>
+        <v>0.0005744197405874729</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.04445688799023628</v>
+        <v>0.0007088948041200638</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.03243640437722206</v>
+        <v>0.0003199924831278622</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.03708391636610031</v>
+        <v>0.000218099114135839</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.02111539244651794</v>
+        <v>0.000230376492254436</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.1981569677591324</v>
+        <v>0.0003560222685337067</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.08117071539163589</v>
+        <v>0.0008366114925593138</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.08151261508464813</v>
+        <v>7.250957423821092e-06</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.04652849957346916</v>
+        <v>0.0003778692916966975</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.0507485419511795</v>
+        <v>0.0008271232945844531</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.1670603603124619</v>
+        <v>7.381744217127562e-05</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.004611998796463013</v>
+        <v>3.61584679922089e-05</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.1329149603843689</v>
+        <v>0.0001999756350414827</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.07007399201393127</v>
+        <v>0.0008801946532912552</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.00811186246573925</v>
+        <v>0.0002388385619269684</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.002822510898113251</v>
+        <v>0.0009830177295953035</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.01472650188952684</v>
+        <v>0.0003143130161333829</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.06302478909492493</v>
+        <v>9.559124009683728e-06</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.07564675807952881</v>
+        <v>0.0001216001837747172</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.08631682395935059</v>
+        <v>0.000496614957228303</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.003967057913541794</v>
+        <v>7.598409138154238e-05</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.07963847368955612</v>
+        <v>0.0006260983645915985</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.03416407853364944</v>
+        <v>0.0006230929284356534</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.1198412552475929</v>
+        <v>0.0007234899094328284</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.1062239557504654</v>
+        <v>0.0001179025712190196</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.05669797211885452</v>
+        <v>6.752656190656126e-06</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.03157187253236771</v>
+        <v>0.0008617931744083762</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.01704712957143784</v>
+        <v>0.0004593680787365884</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.07485699653625488</v>
+        <v>0.000397210504161194</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.03099219128489494</v>
+        <v>4.528595309238881e-05</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.05505262315273285</v>
+        <v>0.0008032810874283314</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.004712051246315241</v>
+        <v>0.0004792532417923212</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.1342906504869461</v>
+        <v>0.0003079432935919613</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.1546666920185089</v>
+        <v>0.00216709659434855</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.1430119425058365</v>
+        <v>0.001575650763697922</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.4363366663455963</v>
+        <v>6.289601151365787e-05</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.1474297493696213</v>
+        <v>0.002463521435856819</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.03475146740674973</v>
+        <v>0.001232174807228148</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.08580455929040909</v>
+        <v>0.0006898834835737944</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.1203848198056221</v>
+        <v>0.0004629384493455291</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.02083909884095192</v>
+        <v>0.0001335847191512585</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.1112759709358215</v>
+        <v>0.00134639535099268</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.2709969282150269</v>
+        <v>0.001332402229309082</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.01673185452818871</v>
+        <v>0.001055056462064385</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.1088231205940247</v>
+        <v>0.0006116122240200639</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.2891023457050323</v>
+        <v>0.001365508884191513</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.02543116174638271</v>
+        <v>0.0003217388293705881</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.2100076377391815</v>
+        <v>1.609985156392213e-05</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.180729553103447</v>
+        <v>0.0007467556861229241</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.03905508294701576</v>
+        <v>0.0001308145438088104</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.1594001948833466</v>
+        <v>0.5417460799217224</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7114303708076477</v>
+        <v>1.383350133895874</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01077170297503471</v>
+        <v>0.4206728041172028</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01940236240625381</v>
+        <v>0.2264861613512039</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2609218060970306</v>
+        <v>0.2918416857719421</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1825795322656631</v>
+        <v>0.1560987234115601</v>
       </c>
       <c r="G11" t="n">
-        <v>0.09918812662363052</v>
+        <v>0.00535811111330986</v>
       </c>
       <c r="H11" t="n">
-        <v>0.08521964401006699</v>
+        <v>0.0335918590426445</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09781637042760849</v>
+        <v>0.2940768301486969</v>
       </c>
       <c r="J11" t="n">
-        <v>0.05450309067964554</v>
+        <v>0.4605520963668823</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4785077273845673</v>
+        <v>1.826003313064575</v>
       </c>
       <c r="L11" t="n">
-        <v>0.068739153444767</v>
+        <v>0.5647476315498352</v>
       </c>
       <c r="M11" t="n">
-        <v>0.006039654836058617</v>
+        <v>0.3172847926616669</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4835624098777771</v>
+        <v>0.4308039247989655</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1929700970649719</v>
+        <v>0.1689725071191788</v>
       </c>
       <c r="P11" t="n">
-        <v>0.05670243129134178</v>
+        <v>0.1916409581899643</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3567955195903778</v>
+        <v>0.1112602800130844</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1024420037865639</v>
+        <v>0.4575756788253784</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0315406322479248</v>
+        <v>0.11672043800354</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3226701319217682</v>
+        <v>0.0671231746673584</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1057611703872681</v>
+        <v>0.06897695362567902</v>
       </c>
       <c r="V11" t="n">
-        <v>0.05253714323043823</v>
+        <v>0.01603825390338898</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1286153346300125</v>
+        <v>0.07719157636165619</v>
       </c>
       <c r="X11" t="n">
-        <v>0.2011764049530029</v>
+        <v>0.04395107179880142</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.06075892597436905</v>
+        <v>0.02781176567077637</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.1024771183729172</v>
+        <v>0.1435878276824951</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.05645215883851051</v>
+        <v>0.3081299364566803</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.09115652740001678</v>
+        <v>0.1905148178339005</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.119327686727047</v>
+        <v>0.007781445980072021</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.07576917111873627</v>
+        <v>0.1770439743995667</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.1429377794265747</v>
+        <v>0.08474753797054291</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.2190481275320053</v>
+        <v>0.1609031558036804</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.2318126112222672</v>
+        <v>0.272230327129364</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.1563970744609833</v>
+        <v>0.1462764739990234</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.1477002650499344</v>
+        <v>0.04721086099743843</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.04580440372228622</v>
+        <v>0.1711732745170593</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.1687793135643005</v>
+        <v>0.08954410254955292</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.2157318443059921</v>
+        <v>0.2191703319549561</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.02741460129618645</v>
+        <v>0.1692011505365372</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.09001287817955017</v>
+        <v>0.1079875081777573</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.06737054139375687</v>
+        <v>0.2329676300287247</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.173184335231781</v>
+        <v>0.01904517970979214</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.108554296195507</v>
+        <v>0.08600842207670212</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.1086841076612473</v>
+        <v>0.01278050057590008</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.06257463991641998</v>
+        <v>0.01566629484295845</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.2406843900680542</v>
+        <v>0.1761983186006546</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.7128025889396667</v>
+        <v>0.5652958154678345</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.049127247184515</v>
+        <v>0.1489318609237671</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.1463181972503662</v>
+        <v>0.1489485204219818</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.3153400421142578</v>
+        <v>0.4358696639537811</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.0507129542529583</v>
+        <v>0.007552165538072586</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.1073432117700577</v>
+        <v>0.03155853971838951</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.1709844172000885</v>
+        <v>0.1441950350999832</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.1492420732975006</v>
+        <v>0.09038947522640228</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.1453688442707062</v>
+        <v>0.3063226044178009</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.009584458544850349</v>
+        <v>0.3134631514549255</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.0116177499294281</v>
+        <v>0.3598628342151642</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.06249229609966278</v>
+        <v>0.1624409854412079</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.3217241764068604</v>
+        <v>0.09859216213226318</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.009277499280869961</v>
+        <v>0.1547481715679169</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.00991395115852356</v>
+        <v>0.0009741270914673805</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.3014340996742249</v>
+        <v>0.1668483912944794</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.1336510330438614</v>
+        <v>0.05975468084216118</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.01566735282540321</v>
+        <v>0.1129148006439209</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.3058033287525177</v>
+        <v>0.1995368897914886</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.03481972217559814</v>
+        <v>0.1226268112659454</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.3818484544754028</v>
+        <v>0.1204096227884293</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.5215336084365845</v>
+        <v>0.2426415383815765</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.1929159462451935</v>
+        <v>0.04555472731590271</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.1028324440121651</v>
+        <v>0.01024152524769306</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.3116129338741302</v>
+        <v>0.1204536333680153</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.1410498917102814</v>
+        <v>0.07426853477954865</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.1581361889839172</v>
+        <v>0.06000378727912903</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.4315388202667236</v>
+        <v>0.5075758695602417</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.06265336275100708</v>
+        <v>0.01000432670116425</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.1105078607797623</v>
+        <v>0.02219041809439659</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.05846350640058517</v>
+        <v>0.02241409197449684</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.05500297248363495</v>
+        <v>0.01424060016870499</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.2222920060157776</v>
+        <v>0.1549693942070007</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.09807175397872925</v>
+        <v>0.03061751462519169</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.01098230481147766</v>
+        <v>0.2574832439422607</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.02193270623683929</v>
+        <v>0.149431899189949</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.1043534576892853</v>
+        <v>0.4107470810413361</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.001016783993691206</v>
+        <v>0.1120475828647614</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.06474339962005615</v>
+        <v>0.02716893330216408</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.004713361151516438</v>
+        <v>0.02554366737604141</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.04088373109698296</v>
+        <v>0.1803410947322845</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.001175301149487495</v>
+        <v>0.0252176932990551</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.0004828779492527246</v>
+        <v>0.115823969244957</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.003652884857729077</v>
+        <v>0.07068602740764618</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.2428084909915924</v>
+        <v>0.02371197193861008</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.1674774289131165</v>
+        <v>0.6165489554405212</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.006460130214691162</v>
+        <v>0.1127891093492508</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.0193568654358387</v>
+        <v>0.04867789894342422</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.547415018081665</v>
+        <v>0.1361821293830872</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.01770417392253876</v>
+        <v>0.2787155508995056</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.07392217218875885</v>
+        <v>0.1067696809768677</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.00333897490054369</v>
+        <v>0.0718185156583786</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.1161284670233727</v>
+        <v>0.001102423295378685</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.01221847347915173</v>
+        <v>0.1392533034086227</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.1030282974243164</v>
+        <v>0.443311333656311</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.001846309984102845</v>
+        <v>0.1077924966812134</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.09977249056100845</v>
+        <v>0.04674451798200607</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.006673175375908613</v>
+        <v>0.02615283988416195</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.1227684691548347</v>
+        <v>0.1678220629692078</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.01316055469214916</v>
+        <v>0.003574661910533905</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.03862191364169121</v>
+        <v>0.08544636517763138</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.01598230749368668</v>
+        <v>0.1356688737869263</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.316582053899765</v>
+        <v>0.2887156009674072</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.7528873085975647</v>
+        <v>0.781471848487854</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.02467225305736065</v>
+        <v>0.01850604265928268</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.1729628145694733</v>
+        <v>0.5458640456199646</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.06565491110086441</v>
+        <v>0.01753858104348183</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.3511962294578552</v>
+        <v>0.5578958988189697</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.2670928239822388</v>
+        <v>0.01475902646780014</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.101970911026001</v>
+        <v>0.1247212961316109</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.2001711428165436</v>
+        <v>0.2258597612380981</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.1697846353054047</v>
+        <v>0.02334499359130859</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.222609281539917</v>
+        <v>0.2505971491336823</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.09957332164049149</v>
+        <v>0.1773297041654587</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.119606539607048</v>
+        <v>0.1319615691900253</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.09595672786235809</v>
+        <v>0.07845215499401093</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.02606700547039509</v>
+        <v>0.1148147433996201</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.08181335031986237</v>
+        <v>0.10603266954422</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.1810568869113922</v>
+        <v>0.2555043399333954</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.1306178569793701</v>
+        <v>0.09433775395154953</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.0787089616060257</v>
+        <v>0.3274560570716858</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.04809901118278503</v>
+        <v>0.1763612329959869</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.0930139571428299</v>
+        <v>0.09303337335586548</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.208336278796196</v>
+        <v>0.07501812279224396</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.1461500823497772</v>
+        <v>0.2371278405189514</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.06669134646654129</v>
+        <v>0.3641000092029572</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.1059281155467033</v>
+        <v>0.1331982612609863</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.0182699803262949</v>
+        <v>0.3658502101898193</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.1124081984162331</v>
+        <v>0.2781524956226349</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.1246560513973236</v>
+        <v>0.03190211951732635</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.1733247637748718</v>
+        <v>0.3290744423866272</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.02705996483564377</v>
+        <v>0.0686970129609108</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.0694003701210022</v>
+        <v>0.08526325970888138</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.02321023866534233</v>
+        <v>0.01515084877610207</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.1504146605730057</v>
+        <v>0.2536323070526123</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.05759788304567337</v>
+        <v>0.009588971734046936</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.008920223452150822</v>
+        <v>0.1063642725348473</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.01444581337273121</v>
+        <v>0.0624229721724987</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.05735998228192329</v>
+        <v>0.08540375530719757</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.03552058339118958</v>
+        <v>0.2473845928907394</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.007013141177594662</v>
+        <v>0.01121982559561729</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.02521643415093422</v>
+        <v>0.145227462053299</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.08213234692811966</v>
+        <v>0.01008261367678642</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.1530995517969131</v>
+        <v>0.1956660002470016</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.003593575209379196</v>
+        <v>0.1506598144769669</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.1195993945002556</v>
+        <v>0.1176846325397491</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.0444938912987709</v>
+        <v>0.02687700465321541</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.02607498504221439</v>
+        <v>0.1490083932876587</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.0821385532617569</v>
+        <v>0.5033524632453918</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.01164260320365429</v>
+        <v>0.1035488098859787</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.0956912636756897</v>
+        <v>0.00398600846529007</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.03657880797982216</v>
+        <v>0.05127647519111633</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.09088942408561707</v>
+        <v>0.1817307323217392</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.003822937607765198</v>
+        <v>0.01297215186059475</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.04960427433252335</v>
+        <v>0.05030828714370728</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.003628951497375965</v>
+        <v>0.1560546159744263</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.163470596075058</v>
+        <v>0.1115278676152229</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.1555252522230148</v>
+        <v>0.0839323103427887</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.003872884437441826</v>
+        <v>0.2254684269428253</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.04553199931979179</v>
+        <v>0.06930030137300491</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.04545930027961731</v>
+        <v>0.2089788466691971</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.01547372061759233</v>
+        <v>0.08681408315896988</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.0342058464884758</v>
+        <v>0.1108066588640213</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.04942430928349495</v>
+        <v>0.1664108037948608</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.03523491322994232</v>
+        <v>0.08314982801675797</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.005289349239319563</v>
+        <v>0.1786587983369827</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.007236214354634285</v>
+        <v>0.1694061309099197</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.05123104527592659</v>
+        <v>0.4082869589328766</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.4725251197814941</v>
+        <v>0.1689415276050568</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.2511544823646545</v>
+        <v>0.3645759522914886</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.01780703663825989</v>
+        <v>0.2085812538862228</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.1424196362495422</v>
+        <v>0.08195273578166962</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.05518077313899994</v>
+        <v>0.1733434498310089</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.08668035268783569</v>
+        <v>0.3885267674922943</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.005313660949468613</v>
+        <v>0.112762413918972</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.2390341609716415</v>
+        <v>0.3442201614379883</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.008294349536299706</v>
+        <v>0.1543712913990021</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.3093514442443848</v>
+        <v>0.07395853847265244</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.4736058413982391</v>
+        <v>0.2869670987129211</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.1229735612869263</v>
+        <v>0.168002724647522</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.2809576988220215</v>
+        <v>0.1069008186459541</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.3141095042228699</v>
+        <v>0.0477677583694458</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.03692185878753662</v>
+        <v>0.2854010462760925</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.03202152997255325</v>
+        <v>0.1357372403144836</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4120293259620667</v>
+        <v>0.3655132651329041</v>
       </c>
       <c r="C12" t="n">
-        <v>0.03167087212204933</v>
+        <v>0.09243419766426086</v>
       </c>
       <c r="D12" t="n">
-        <v>0.05647751688957214</v>
+        <v>0.09276292473077774</v>
       </c>
       <c r="E12" t="n">
-        <v>0.07683198899030685</v>
+        <v>0.2681815028190613</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0632869079709053</v>
+        <v>0.2942537665367126</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3617803752422333</v>
+        <v>0.1865312457084656</v>
       </c>
       <c r="H12" t="n">
-        <v>0.01274015661329031</v>
+        <v>0.08047622442245483</v>
       </c>
       <c r="I12" t="n">
-        <v>0.007396966684609652</v>
+        <v>0.1696131229400635</v>
       </c>
       <c r="J12" t="n">
-        <v>0.01704315096139908</v>
+        <v>0.1337011605501175</v>
       </c>
       <c r="K12" t="n">
-        <v>0.287567675113678</v>
+        <v>0.5076099634170532</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02240083180367947</v>
+        <v>0.01615500450134277</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2016577422618866</v>
+        <v>0.07873377203941345</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1193272694945335</v>
+        <v>0.2816720008850098</v>
       </c>
       <c r="O12" t="n">
-        <v>0.07813151925802231</v>
+        <v>0.1339074671268463</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2986744344234467</v>
+        <v>0.2517101764678955</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0811370313167572</v>
+        <v>0.05122929438948631</v>
       </c>
       <c r="R12" t="n">
-        <v>0.05957577750086784</v>
+        <v>0.06721579283475876</v>
       </c>
       <c r="S12" t="n">
-        <v>0.06052245199680328</v>
+        <v>0.01707259379327297</v>
       </c>
       <c r="T12" t="n">
-        <v>0.122934378683567</v>
+        <v>0.01406819839030504</v>
       </c>
       <c r="U12" t="n">
-        <v>0.000717568676918745</v>
+        <v>0.03364838659763336</v>
       </c>
       <c r="V12" t="n">
-        <v>0.05688845366239548</v>
+        <v>0.01113400422036648</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1400912702083588</v>
+        <v>0.0505874790251255</v>
       </c>
       <c r="X12" t="n">
-        <v>0.06077477335929871</v>
+        <v>0.06789986044168472</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.04169543832540512</v>
+        <v>0.07954347878694534</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.008054062724113464</v>
+        <v>0.01131877116858959</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.01764188520610332</v>
+        <v>0.01404037326574326</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.05512269586324692</v>
+        <v>0.02879790961742401</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1031273454427719</v>
+        <v>0.07740022987127304</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.0001088501885533333</v>
+        <v>0.2020117044448853</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.01593105867505074</v>
+        <v>0.066011942923069</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.02598681300878525</v>
+        <v>0.0940508171916008</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.02178504690527916</v>
+        <v>0.03777528554201126</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.02768911607563496</v>
+        <v>0.04125137999653816</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.01294009014964104</v>
+        <v>0.1173965856432915</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.02537832409143448</v>
+        <v>0.05731955170631409</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.04690762236714363</v>
+        <v>0.05980779975652695</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.03456106409430504</v>
+        <v>0.260130375623703</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.008638396859169006</v>
+        <v>0.03355435281991959</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.05516733229160309</v>
+        <v>0.01220972836017609</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.004018325358629227</v>
+        <v>0.1437421441078186</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.03975450992584229</v>
+        <v>0.07745596021413803</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.04298318177461624</v>
+        <v>0.05827146023511887</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.01012210920453072</v>
+        <v>0.04644599929451942</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.01868266426026821</v>
+        <v>0.05892432481050491</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.1333973556756973</v>
+        <v>0.2068115919828415</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.4179752469062805</v>
+        <v>0.502781093120575</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.02198020741343498</v>
+        <v>0.0514882318675518</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.1386392116546631</v>
+        <v>0.1075455695390701</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.1065112426877022</v>
+        <v>0.009188232943415642</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.0121153611689806</v>
+        <v>0.07474866509437561</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.1245549470186234</v>
+        <v>0.001395951956510544</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.08439763635396957</v>
+        <v>0.08402042090892792</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.00281347194686532</v>
+        <v>0.02691496908664703</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.02670378983020782</v>
+        <v>0.0715671107172966</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.07158380746841431</v>
+        <v>0.2165826857089996</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.1447479277849197</v>
+        <v>0.07204438745975494</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.08359038829803467</v>
+        <v>0.04348454996943474</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.1220321655273438</v>
+        <v>0.286731481552124</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.09823747724294662</v>
+        <v>0.04834445938467979</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.1510773450136185</v>
+        <v>0.06356603652238846</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.07466083765029907</v>
+        <v>0.07640563696622849</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.01739213056862354</v>
+        <v>0.07088948041200638</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.01735390350222588</v>
+        <v>0.0296209380030632</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1442637592554092</v>
+        <v>0.05585875734686852</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.06742164492607117</v>
+        <v>0.06046842783689499</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.07014565169811249</v>
+        <v>0.01384095475077629</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.2224603891372681</v>
+        <v>0.07643876969814301</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.04600207135081291</v>
+        <v>0.1451307386159897</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.02677118591964245</v>
+        <v>0.04728661850094795</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.08280111104249954</v>
+        <v>0.03726772964000702</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.01198061648756266</v>
+        <v>0.08715123683214188</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.05871719866991043</v>
+        <v>0.1505014002323151</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1823897659778595</v>
+        <v>0.317876398563385</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.06204183399677277</v>
+        <v>0.01652108691632748</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.08819137513637543</v>
+        <v>0.04433812573552132</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.05149712041020393</v>
+        <v>0.06095264479517937</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.0726461187005043</v>
+        <v>0.1285955905914307</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.01485991477966309</v>
+        <v>0.003953179344534874</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.07835398614406586</v>
+        <v>0.06963825225830078</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.01822922006249428</v>
+        <v>0.03513184189796448</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.01653384044766426</v>
+        <v>0.001823047176003456</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.08622586727142334</v>
+        <v>0.1473095268011093</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.03052207641303539</v>
+        <v>0.01702092960476875</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.05092839896678925</v>
+        <v>0.01621437259018421</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.002534034196287394</v>
+        <v>0.0412309430539608</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.001170761766843498</v>
+        <v>0.1210798695683479</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.06245992332696915</v>
+        <v>0.02404705062508583</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.02076829224824905</v>
+        <v>0.01209417730569839</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.001646274933591485</v>
+        <v>0.04741217941045761</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.1150060668587685</v>
+        <v>0.02270623296499252</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.1686142832040787</v>
+        <v>0.235015794634819</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.02434060536324978</v>
+        <v>0.04688328132033348</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.008996317163109779</v>
+        <v>0.01905995979905128</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.1130455806851387</v>
+        <v>0.1819359511137009</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.05696176737546921</v>
+        <v>0.08428309112787247</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.02250057831406593</v>
+        <v>0.1134461015462875</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.01211290061473846</v>
+        <v>0.06199771910905838</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.03261710330843925</v>
+        <v>0.003138068597763777</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.02418847382068634</v>
+        <v>0.01182801462709904</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.06562357395887375</v>
+        <v>0.1495884954929352</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.05193427577614784</v>
+        <v>0.02745411917567253</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.07560690492391586</v>
+        <v>0.01469890959560871</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.004191011656075716</v>
+        <v>0.06122508645057678</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.007659071125090122</v>
+        <v>0.1171524971723557</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.07142353802919388</v>
+        <v>0.02481741085648537</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.007653830572962761</v>
+        <v>0.02437289990484715</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.004475375171750784</v>
+        <v>0.06867769360542297</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.06691739708185196</v>
+        <v>0.02914594858884811</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.325165331363678</v>
+        <v>0.1387353539466858</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.07482284307479858</v>
+        <v>0.1526474952697754</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.07649575173854828</v>
+        <v>0.09608715772628784</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.05336255580186844</v>
+        <v>0.05155946314334869</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.03769854083657265</v>
+        <v>0.1500737220048904</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.05038608238101006</v>
+        <v>0.04749639704823494</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.0320807509124279</v>
+        <v>0.06889434158802032</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.04141711443662643</v>
+        <v>0.006448785774409771</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.02996387332677841</v>
+        <v>0.02536394074559212</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.06910812854766846</v>
+        <v>0.08195839822292328</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.05222035199403763</v>
+        <v>0.03611398860812187</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.02994927018880844</v>
+        <v>0.1265221685171127</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.05427943542599678</v>
+        <v>0.1164807379245758</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.0287574827671051</v>
+        <v>0.1145122498273849</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.01895634829998016</v>
+        <v>0.09080212563276291</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.002385362517088652</v>
+        <v>0.04816431552171707</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.02271934784948826</v>
+        <v>0.1035723611712456</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.02936676144599915</v>
+        <v>0.02301711216568947</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.04213711246848106</v>
+        <v>0.04049151018261909</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.008668524213135242</v>
+        <v>0.08415356278419495</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.08294368535280228</v>
+        <v>0.03006000816822052</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.04629500955343246</v>
+        <v>0.06871526688337326</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.05357307940721512</v>
+        <v>0.1906635016202927</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.008651267737150192</v>
+        <v>0.03732246905565262</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.04639368876814842</v>
+        <v>0.05824517086148262</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.01891815848648548</v>
+        <v>0.05774208903312683</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.04493359103798866</v>
+        <v>0.02110916189849377</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.01135189924389124</v>
+        <v>0.1554341614246368</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.02323510497808456</v>
+        <v>0.04333441704511642</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.07307868450880051</v>
+        <v>0.0903010368347168</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.0148882893845439</v>
+        <v>0.0008966727182269096</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.005047737620770931</v>
+        <v>0.1090419739484787</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.06008847802877426</v>
+        <v>0.01486601401120424</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.04351184517145157</v>
+        <v>0.004169099498540163</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.005147141870111227</v>
+        <v>0.0425570048391819</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.07042951881885529</v>
+        <v>0.1104427874088287</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.02720521204173565</v>
+        <v>0.1158490255475044</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.08553650230169296</v>
+        <v>0.0398581437766552</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.07881848514080048</v>
+        <v>0.09934218972921371</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.01275178510695696</v>
+        <v>0.07348323613405228</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.06524158269166946</v>
+        <v>0.01792087405920029</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.05062544345855713</v>
+        <v>0.01609413139522076</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.07015904784202576</v>
+        <v>0.04734824970364571</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.0128922127187252</v>
+        <v>0.01330688409507275</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.02145938389003277</v>
+        <v>0.01583991572260857</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.06024040281772614</v>
+        <v>0.1588541269302368</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.03610906377434731</v>
+        <v>0.05013611167669296</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.05784478038549423</v>
+        <v>0.03799142688512802</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.003358903806656599</v>
+        <v>0.05116082355380058</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.008943488821387291</v>
+        <v>0.09073583036661148</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.07372679561376572</v>
+        <v>0.01686684973537922</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.02106412500143051</v>
+        <v>0.0241207629442215</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.0005860504461452365</v>
+        <v>0.07016012817621231</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.0691523477435112</v>
+        <v>0.1818358451128006</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.01251340005546808</v>
+        <v>0.09014837443828583</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.02103705145418644</v>
+        <v>0.06813664734363556</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.07994979619979858</v>
+        <v>0.1010923609137535</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.07303167134523392</v>
+        <v>0.1055142283439636</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.0308922566473484</v>
+        <v>0.02575615048408508</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.02243681810796261</v>
+        <v>0.02538632601499557</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.009359539486467838</v>
+        <v>0.05867919698357582</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.002413187175989151</v>
+        <v>0.1771826595067978</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.04145076870918274</v>
+        <v>0.01049806177616119</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.0583668127655983</v>
+        <v>0.3329670131206512</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.06209652498364449</v>
+        <v>0.1951156705617905</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.03931978344917297</v>
+        <v>0.04268845915794373</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.08071506023406982</v>
+        <v>0.1914508044719696</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.003762019332498312</v>
+        <v>0.3233496844768524</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.06798775494098663</v>
+        <v>0.1380466967821121</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.0344778373837471</v>
+        <v>0.09107838571071625</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.03449530526995659</v>
+        <v>0.03374244645237923</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.06221781671047211</v>
+        <v>0.0185718722641468</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.07519048452377319</v>
+        <v>0.1125242412090302</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.03015079721808434</v>
+        <v>0.00997590646147728</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.1011781394481659</v>
+        <v>0.04407469555735588</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.03028763644397259</v>
+        <v>0.05389397591352463</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.08583275973796844</v>
+        <v>0.01983540877699852</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.05176468566060066</v>
+        <v>0.06677167117595673</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.1052422747015953</v>
+        <v>0.06266333907842636</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.01237213518470526</v>
+        <v>0.001658849301747978</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.02035979554057121</v>
+        <v>0.1792710721492767</v>
       </c>
       <c r="B13" t="n">
-        <v>0.3350856006145477</v>
+        <v>0.09020590037107468</v>
       </c>
       <c r="C13" t="n">
-        <v>0.04815386608242989</v>
+        <v>0.01567168906331062</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1102675199508667</v>
+        <v>0.1679465770721436</v>
       </c>
       <c r="E13" t="n">
-        <v>0.07051281630992889</v>
+        <v>0.3328409194946289</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0268617756664753</v>
+        <v>0.4681041538715363</v>
       </c>
       <c r="G13" t="n">
-        <v>0.01739689894020557</v>
+        <v>0.1720890551805496</v>
       </c>
       <c r="H13" t="n">
-        <v>0.01562019437551498</v>
+        <v>0.3060674369335175</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1100106090307236</v>
+        <v>0.1690121293067932</v>
       </c>
       <c r="J13" t="n">
-        <v>0.03038249164819717</v>
+        <v>0.121514305472374</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2536068558692932</v>
+        <v>0.308561384677887</v>
       </c>
       <c r="L13" t="n">
-        <v>0.001562192686833441</v>
+        <v>0.005373075604438782</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1082296893000603</v>
+        <v>0.0198585893958807</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1079478859901428</v>
+        <v>0.276744931936264</v>
       </c>
       <c r="O13" t="n">
-        <v>0.05074142664670944</v>
+        <v>0.5552907586097717</v>
       </c>
       <c r="P13" t="n">
-        <v>0.04321766272187233</v>
+        <v>0.2837556004524231</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.04629851132631302</v>
+        <v>0.001182926818728447</v>
       </c>
       <c r="R13" t="n">
-        <v>0.09474283456802368</v>
+        <v>0.1473231166601181</v>
       </c>
       <c r="S13" t="n">
-        <v>0.005968877580016851</v>
+        <v>0.1396618485450745</v>
       </c>
       <c r="T13" t="n">
-        <v>0.07424578815698624</v>
+        <v>0.01128668151795864</v>
       </c>
       <c r="U13" t="n">
-        <v>0.055008415132761</v>
+        <v>0.06437890231609344</v>
       </c>
       <c r="V13" t="n">
-        <v>0.03829576075077057</v>
+        <v>0.3476381301879883</v>
       </c>
       <c r="W13" t="n">
-        <v>0.004754167050123215</v>
+        <v>0.3465553820133209</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0550139993429184</v>
+        <v>0.1040186136960983</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.02323459275066853</v>
+        <v>0.03555737435817719</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.003244840074330568</v>
+        <v>0.1093786731362343</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.02408170141279697</v>
+        <v>0.1282013803720474</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.02849896438419819</v>
+        <v>0.03204404935240746</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.05994182080030441</v>
+        <v>0.2338831871747971</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.01068565715104342</v>
+        <v>0.01866498216986656</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.02764646708965302</v>
+        <v>0.0935530960559845</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.006209780462086201</v>
+        <v>0.1976762115955353</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.01715721189975739</v>
+        <v>0.09621788561344147</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.02014704793691635</v>
+        <v>0.03423383831977844</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.03461076691746712</v>
+        <v>0.4010193943977356</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.01365993916988373</v>
+        <v>0.04173152521252632</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.03520119935274124</v>
+        <v>0.1040709540247917</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.03689036890864372</v>
+        <v>0.1501842588186264</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.02620916813611984</v>
+        <v>0.08361548185348511</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.007094230502843857</v>
+        <v>0.2075652778148651</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.01676273532211781</v>
+        <v>0.09125594794750214</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.03260551393032074</v>
+        <v>0.04887054488062859</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.01319205109030008</v>
+        <v>0.07692119479179382</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.01150153204798698</v>
+        <v>0.1028375551104546</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.01110518630594015</v>
+        <v>0.05434949323534966</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.02235452644526958</v>
+        <v>0.01621188223361969</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.2706342339515686</v>
+        <v>0.9470763802528381</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.01270570140331984</v>
+        <v>0.07635654509067535</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.006108895875513554</v>
+        <v>0.03017868846654892</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.01539941690862179</v>
+        <v>0.1173093616962433</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.0108812227845192</v>
+        <v>0.2056345045566559</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.03249221667647362</v>
+        <v>0.09416734427213669</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.01011626981198788</v>
+        <v>0.09298675507307053</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.02223019674420357</v>
+        <v>0.03732930868864059</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.01875507459044456</v>
+        <v>0.1209340170025826</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.07730141282081604</v>
+        <v>0.3728393912315369</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.05120494589209557</v>
+        <v>0.05553652718663216</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.006653555203229189</v>
+        <v>0.2023934721946716</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.09892905503511429</v>
+        <v>0.2965115606784821</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.06079233810305595</v>
+        <v>0.07110799849033356</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.00278730783611536</v>
+        <v>0.08107534795999527</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.04744256660342216</v>
+        <v>0.2005897164344788</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.0384330078959465</v>
+        <v>0.0155483465641737</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.03605088964104652</v>
+        <v>0.07567133009433746</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.07606104761362076</v>
+        <v>0.3080192804336548</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.03130130469799042</v>
+        <v>0.01652925275266171</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.002813022583723068</v>
+        <v>0.1361101269721985</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.1209314465522766</v>
+        <v>0.196090966463089</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.06548583507537842</v>
+        <v>0.1472716331481934</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.006466974504292011</v>
+        <v>0.4742016196250916</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.02405814826488495</v>
+        <v>0.06583984196186066</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.002571171149611473</v>
+        <v>0.02359655313193798</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.01235225144773722</v>
+        <v>0.03456948325037956</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.1519585400819778</v>
+        <v>0.3548827171325684</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.03065736964344978</v>
+        <v>0.0872655063867569</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.02832235395908356</v>
+        <v>0.3030792474746704</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.03136833012104034</v>
+        <v>0.2509118020534515</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.06879284977912903</v>
+        <v>0.2069911658763885</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.04126575961709023</v>
+        <v>0.03899045661091805</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.00241178460419178</v>
+        <v>0.07530935108661652</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.03639152273535728</v>
+        <v>0.1593343317508698</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.004235429689288139</v>
+        <v>0.04928524792194366</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.06895302981138229</v>
+        <v>0.1030922383069992</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.003615407971665263</v>
+        <v>0.002666329964995384</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.02904846891760826</v>
+        <v>0.07372525334358215</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.01200591959059238</v>
+        <v>0.04041430354118347</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.004493244923651218</v>
+        <v>0.08989088237285614</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.004288928583264351</v>
+        <v>0.112574428319931</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.009773275814950466</v>
+        <v>0.05834178254008293</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.03164901584386826</v>
+        <v>0.01906845718622208</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.09101311862468719</v>
+        <v>0.2409434020519257</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.1222031861543655</v>
+        <v>0.4450185596942902</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.004889439791440964</v>
+        <v>0.1283738166093826</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.02470576390624046</v>
+        <v>0.2274671494960785</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.06852263957262039</v>
+        <v>0.006883440539240837</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.01887046918272972</v>
+        <v>0.02116598933935165</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.02075250074267387</v>
+        <v>0.2495043724775314</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.07878988981246948</v>
+        <v>0.1248554885387421</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.001391325145959854</v>
+        <v>0.0008398555219173431</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.003733065677806735</v>
+        <v>0.09118897467851639</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.05751220881938934</v>
+        <v>0.0545126274228096</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.01651005633175373</v>
+        <v>0.007997346110641956</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.03711710125207901</v>
+        <v>0.03011835739016533</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.004728430416435003</v>
+        <v>0.02625694125890732</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.01306977961212397</v>
+        <v>0.08336453884840012</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.005489956121891737</v>
+        <v>0.04249106347560883</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.003866754472255707</v>
+        <v>0.0415063165128231</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.02449613995850086</v>
+        <v>0.01843238435685635</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.05405046418309212</v>
+        <v>0.2583600580692291</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.1820785254240036</v>
+        <v>0.09067412465810776</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.04251736029982567</v>
+        <v>0.03448415547609329</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.1137884259223938</v>
+        <v>0.3099268972873688</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.01565367169678211</v>
+        <v>0.04869810119271278</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.01222987659275532</v>
+        <v>0.003008400090038776</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.102142333984375</v>
+        <v>0.1025521159172058</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.02774490229785442</v>
+        <v>0.4162740111351013</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.04336804524064064</v>
+        <v>0.06751927733421326</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.02956178039312363</v>
+        <v>0.09669709950685501</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.0387343093752861</v>
+        <v>0.06708041578531265</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.03551370650529861</v>
+        <v>0.03435468301177025</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.02975969389081001</v>
+        <v>0.2521009147167206</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.02425025403499603</v>
+        <v>0.03338039666414261</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.01233544293791056</v>
+        <v>0.02914353273808956</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.04764612764120102</v>
+        <v>0.01759866252541542</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.006896441802382469</v>
+        <v>0.04395890608429909</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.01196455396711826</v>
+        <v>0.03030220977962017</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.0211947001516819</v>
+        <v>0.03240611031651497</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.02717102132737637</v>
+        <v>0.1931508928537369</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.02085299603641033</v>
+        <v>0.1496217250823975</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.04624374583363533</v>
+        <v>0.1275180578231812</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.053998913615942</v>
+        <v>0.2237505465745926</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.01304395962506533</v>
+        <v>0.1559199839830399</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.03956753015518188</v>
+        <v>0.03849075734615326</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.03259143605828285</v>
+        <v>0.1226433664560318</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.01880100555717945</v>
+        <v>0.0882653146982193</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.00834253802895546</v>
+        <v>0.01333621144294739</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.01171031780540943</v>
+        <v>0.1558165848255157</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.003957452718168497</v>
+        <v>0.06384724378585815</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.02420861274003983</v>
+        <v>0.08649740368127823</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.01476518902927637</v>
+        <v>0.04879648983478546</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.005709502846002579</v>
+        <v>0.0937519446015358</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.02181311324238777</v>
+        <v>0.0484931692481041</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.007843027822673321</v>
+        <v>0.03520575165748596</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.03305971249938011</v>
+        <v>0.03333204984664917</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.03245814144611359</v>
+        <v>0.01454467326402664</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.03796491771936417</v>
+        <v>0.04404339194297791</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.02512296289205551</v>
+        <v>0.08623477071523666</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.03146953508257866</v>
+        <v>0.0005402378737926483</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.02343419194221497</v>
+        <v>0.03419199585914612</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.04360828548669815</v>
+        <v>0.002332646865397692</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.02428177930414677</v>
+        <v>0.123303197324276</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.03071718104183674</v>
+        <v>0.1987239122390747</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.0188586637377739</v>
+        <v>0.1393558233976364</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.0004058233462274075</v>
+        <v>0.07524041831493378</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.06357016414403915</v>
+        <v>0.1147273257374763</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.006716723553836346</v>
+        <v>0.0210338830947876</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.03132712841033936</v>
+        <v>0.006731332279741764</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.006032389588654041</v>
+        <v>0.03312256187200546</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.02056404203176498</v>
+        <v>0.09436924010515213</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.008249546401202679</v>
+        <v>0.1206977069377899</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.01058747712522745</v>
+        <v>0.03244573995471001</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.02203674986958504</v>
+        <v>0.03913068771362305</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.01899645291268826</v>
+        <v>0.09158490598201752</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.03544459119439125</v>
+        <v>0.1362022161483765</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.002488539088517427</v>
+        <v>0.09830325096845627</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.0199850108474493</v>
+        <v>0.1874887347221375</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.03599778562784195</v>
+        <v>0.1447990536689758</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.009627986699342728</v>
+        <v>0.01875322498381138</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.02092187851667404</v>
+        <v>0.08937592804431915</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.01895917020738125</v>
+        <v>0.2523383498191833</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.04937678202986717</v>
+        <v>0.1349698007106781</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.02519509382545948</v>
+        <v>0.1601311564445496</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.02334164828062057</v>
+        <v>0.2262720465660095</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.05272243544459343</v>
+        <v>0.1196698993444443</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.03112149983644485</v>
+        <v>0.1103852912783623</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.04976264387369156</v>
+        <v>0.2552951574325562</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.04649670049548149</v>
+        <v>0.1142438799142838</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.00138571672141552</v>
+        <v>0.03996420279145241</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.01417579129338264</v>
+        <v>0.273038387298584</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.01744465902447701</v>
+        <v>0.1404884457588196</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.01765574142336845</v>
+        <v>0.1230618432164192</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.08075903356075287</v>
+        <v>0.1758081465959549</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.03268879652023315</v>
+        <v>0.08852432668209076</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.03718594834208488</v>
+        <v>0.03455942869186401</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.06525837630033493</v>
+        <v>0.1510166078805923</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.04364141076803207</v>
+        <v>0.1664855182170868</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.04629956185817719</v>
+        <v>0.01765533909201622</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.01245541125535965</v>
+        <v>0.1096956506371498</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.001057294197380543</v>
+        <v>0.04591618105769157</v>
       </c>
     </row>
     <row r="14">
@@ -8396,1709 +8396,1709 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.07736712694168091</v>
+        <v>0.3075096309185028</v>
       </c>
       <c r="B15" t="n">
-        <v>0.535087525844574</v>
+        <v>0.5440521240234375</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5887497663497925</v>
+        <v>0.4998429417610168</v>
       </c>
       <c r="D15" t="n">
-        <v>0.200050950050354</v>
+        <v>0.1342508345842361</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4043194055557251</v>
+        <v>0.2733323574066162</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1701971590518951</v>
+        <v>0.03712362796068192</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2252794951200485</v>
+        <v>0.2168353497982025</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3002480566501617</v>
+        <v>0.2302380353212357</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3935266137123108</v>
+        <v>0.05571899935603142</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1303516328334808</v>
+        <v>0.2064643204212189</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4743126034736633</v>
+        <v>0.5928605198860168</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3461591005325317</v>
+        <v>0.5036376714706421</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1262057274580002</v>
+        <v>0.05364594608545303</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4678476750850677</v>
+        <v>0.3227912187576294</v>
       </c>
       <c r="O15" t="n">
-        <v>0.20347860455513</v>
+        <v>0.09117679297924042</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1361256837844849</v>
+        <v>0.2911801338195801</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.2301888018846512</v>
+        <v>0.1109380722045898</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3490595519542694</v>
+        <v>0.02531002089381218</v>
       </c>
       <c r="S15" t="n">
-        <v>0.05930811539292336</v>
+        <v>0.1573041379451752</v>
       </c>
       <c r="T15" t="n">
-        <v>0.05001415312290192</v>
+        <v>0.1396782845258713</v>
       </c>
       <c r="U15" t="n">
-        <v>0.03093219175934792</v>
+        <v>0.1006611436605453</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2383191585540771</v>
+        <v>0.1622200161218643</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2092477381229401</v>
+        <v>0.02100059203803539</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1023428291082382</v>
+        <v>0.02138445526361465</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.002772317500784993</v>
+        <v>0.02369947917759418</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.156458392739296</v>
+        <v>0.04567499458789825</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.06707453727722168</v>
+        <v>0.1500275284051895</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.1077054888010025</v>
+        <v>0.2578504383563995</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.1347696185112</v>
+        <v>0.1145711541175842</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.0006769020110368729</v>
+        <v>0.08425737917423248</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.08565618097782135</v>
+        <v>0.3425913155078888</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.1237465143203735</v>
+        <v>0.05055206641554832</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.2401780039072037</v>
+        <v>0.2268794327974319</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.05884630978107452</v>
+        <v>0.1534490287303925</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.08949511498212814</v>
+        <v>0.426946759223938</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.1269604414701462</v>
+        <v>0.1741346567869186</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.01396337896585464</v>
+        <v>0.1120034903287888</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.2671281397342682</v>
+        <v>0.3572457432746887</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.06678225100040436</v>
+        <v>0.03293028846383095</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.08147702366113663</v>
+        <v>0.002198303584009409</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.0295839998871088</v>
+        <v>0.4141143262386322</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.1899004578590393</v>
+        <v>0.07360725104808807</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.005856219679117203</v>
+        <v>0.04189394041895866</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.05817036330699921</v>
+        <v>0.1386286914348602</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.08128494024276733</v>
+        <v>0.05648998916149139</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.1178359985351562</v>
+        <v>0.07593406736850739</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.2896538376808167</v>
+        <v>0.7808860540390015</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.3818565607070923</v>
+        <v>0.1502117663621902</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.06650618463754654</v>
+        <v>0.03638713806867599</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.2499396353960037</v>
+        <v>0.0002655759453773499</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.1582468748092651</v>
+        <v>0.03611081838607788</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.05589266121387482</v>
+        <v>0.02277805469930172</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.1726583689451218</v>
+        <v>0.1564146280288696</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.02567137964069843</v>
+        <v>0.0713045746088028</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.000217018648982048</v>
+        <v>0.1922014355659485</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.123107522726059</v>
+        <v>0.4842360019683838</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.0213792659342289</v>
+        <v>0.325306624174118</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.1793335825204849</v>
+        <v>0.01799233816564083</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.3523169755935669</v>
+        <v>0.4252505898475647</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.09169456362724304</v>
+        <v>0.0009841788560152054</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.1228909716010094</v>
+        <v>0.04501625522971153</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.1179648637771606</v>
+        <v>0.1183338761329651</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.1768305897712708</v>
+        <v>0.04234039783477783</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.1463725715875626</v>
+        <v>0.04677243530750275</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.09029114246368408</v>
+        <v>0.04070012271404266</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.0502593033015728</v>
+        <v>0.07801060378551483</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.1835523843765259</v>
+        <v>0.1679488569498062</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.02256863564252853</v>
+        <v>0.1232034936547279</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.09517841786146164</v>
+        <v>0.016401631757617</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.1409980654716492</v>
+        <v>0.2653965353965759</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.190943643450737</v>
+        <v>0.114224448800087</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.09726282954216003</v>
+        <v>0.1094915568828583</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.1108664572238922</v>
+        <v>0.0188099779188633</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.2310057282447815</v>
+        <v>0.6518538594245911</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.3049452900886536</v>
+        <v>0.08731744438409805</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.06985247135162354</v>
+        <v>0.04920067638158798</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.1112186685204506</v>
+        <v>0.07300594449043274</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.067393459379673</v>
+        <v>0.1138292402029037</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.0554109513759613</v>
+        <v>0.1336741745471954</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.1288936138153076</v>
+        <v>0.07279164344072342</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.07703884690999985</v>
+        <v>0.09537153691053391</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.0182137805968523</v>
+        <v>0.08727115392684937</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.0643598884344101</v>
+        <v>0.2835504412651062</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.07714105397462845</v>
+        <v>0.1298232525587082</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.1252313554286957</v>
+        <v>0.08561194688081741</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.1102650165557861</v>
+        <v>0.04288172721862793</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.009529094211757183</v>
+        <v>0.01795060560107231</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.01494037266820669</v>
+        <v>0.01455886196345091</v>
       </c>
       <c r="CK15" t="n">
-        <v>0.08851441740989685</v>
+        <v>0.06163268536329269</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.05716395750641823</v>
+        <v>0.003486092202365398</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.004291091114282608</v>
+        <v>0.3062742650508881</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.09004276245832443</v>
+        <v>0.343034029006958</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.04572383314371109</v>
+        <v>0.1796933561563492</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.2893356382846832</v>
+        <v>0.229986160993576</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.3446162343025208</v>
+        <v>0.2766178548336029</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.07156749814748764</v>
+        <v>0.07593536376953125</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.2097762525081635</v>
+        <v>0.1830769181251526</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.01701156049966812</v>
+        <v>0.169967845082283</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.09595626592636108</v>
+        <v>0.1078097447752953</v>
       </c>
       <c r="CV15" t="n">
-        <v>0.03542829677462578</v>
+        <v>0.1146179661154747</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.02998174354434013</v>
+        <v>0.2434877902269363</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.07213331013917923</v>
+        <v>0.1308680176734924</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.07379376888275146</v>
+        <v>0.03913156688213348</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.1116764545440674</v>
+        <v>0.04957414045929909</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.05046318843960762</v>
+        <v>0.02823181450366974</v>
       </c>
       <c r="DB15" t="n">
-        <v>0.004727263003587723</v>
+        <v>0.007493112701922655</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.07085932791233063</v>
+        <v>0.03799455985426903</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.1000500693917274</v>
+        <v>0.05702348798513412</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.1906093209981918</v>
+        <v>0.2275114357471466</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.0612415075302124</v>
+        <v>0.1180409640073776</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.1004934906959534</v>
+        <v>0.07008201628923416</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.248759388923645</v>
+        <v>0.1696754992008209</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.110139288008213</v>
+        <v>0.1675584316253662</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.2327811568975449</v>
+        <v>0.3786598742008209</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.1097374856472015</v>
+        <v>0.08883355557918549</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.2444190084934235</v>
+        <v>0.06459147483110428</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.1119900345802307</v>
+        <v>0.1318750828504562</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.06178105250000954</v>
+        <v>0.07535690814256668</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.05457401275634766</v>
+        <v>0.1334993243217468</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.1456043124198914</v>
+        <v>0.1252315789461136</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.1563101261854172</v>
+        <v>0.07095576077699661</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.1006762832403183</v>
+        <v>0.06269916146993637</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.1354936361312866</v>
+        <v>0.1348429620265961</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.09371277689933777</v>
+        <v>0.09275639802217484</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.1538990288972855</v>
+        <v>0.009893829002976418</v>
       </c>
       <c r="DV15" t="n">
-        <v>0.1178280860185623</v>
+        <v>0.05754360556602478</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.04805527627468109</v>
+        <v>0.03843476250767708</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.041342593729496</v>
+        <v>0.1957986950874329</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.1128605455160141</v>
+        <v>0.1589477062225342</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.02738763764500618</v>
+        <v>0.01902572624385357</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.03967134654521942</v>
+        <v>0.1003862395882607</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.1536790430545807</v>
+        <v>0.1102509275078773</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.06769546866416931</v>
+        <v>0.02769501693546772</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.1273731738328934</v>
+        <v>0.1075527891516685</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.03432532027363777</v>
+        <v>0.2020061016082764</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.02809175848960876</v>
+        <v>0.03534124791622162</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.07098209112882614</v>
+        <v>0.09009719640016556</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.03143056482076645</v>
+        <v>0.06821809709072113</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.01256189495325089</v>
+        <v>0.02072983980178833</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.1771583706140518</v>
+        <v>0.02796874195337296</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.08864527940750122</v>
+        <v>0.0408971831202507</v>
       </c>
       <c r="EL15" t="n">
-        <v>0.04325386881828308</v>
+        <v>0.04401130974292755</v>
       </c>
       <c r="EM15" t="n">
-        <v>0.01442631334066391</v>
+        <v>0.05180094018578529</v>
       </c>
       <c r="EN15" t="n">
-        <v>0.1109707579016685</v>
+        <v>0.008924899622797966</v>
       </c>
       <c r="EO15" t="n">
-        <v>0.04065340757369995</v>
+        <v>0.1123715490102768</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.03836233541369438</v>
+        <v>0.2176413387060165</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.04265549778938293</v>
+        <v>0.01200390420854092</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.05444993823766708</v>
+        <v>0.1259057968854904</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.07572041451931</v>
+        <v>0.07918418943881989</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.04760422557592392</v>
+        <v>0.139692559838295</v>
       </c>
       <c r="EU15" t="n">
-        <v>0.08828632533550262</v>
+        <v>0.147602379322052</v>
       </c>
       <c r="EV15" t="n">
-        <v>0.1342185139656067</v>
+        <v>0.04980768263339996</v>
       </c>
       <c r="EW15" t="n">
-        <v>0.3141079843044281</v>
+        <v>0.02441486343741417</v>
       </c>
       <c r="EX15" t="n">
-        <v>0.0194186195731163</v>
+        <v>0.08895207196474075</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.04210305213928223</v>
+        <v>0.2980099320411682</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.06396855413913727</v>
+        <v>0.1201103180646896</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.1275532841682434</v>
+        <v>0.02938249334692955</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.1058608517050743</v>
+        <v>0.06673840433359146</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.05718984827399254</v>
+        <v>0.04541463777422905</v>
       </c>
       <c r="FD15" t="n">
-        <v>0.02541899494826794</v>
+        <v>0.01996393315494061</v>
       </c>
       <c r="FE15" t="n">
-        <v>0.1244166418910027</v>
+        <v>0.0209975577890873</v>
       </c>
       <c r="FF15" t="n">
-        <v>0.03913624212145805</v>
+        <v>0.05245667695999146</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.005319420248270035</v>
+        <v>0.005125625059008598</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.09458860009908676</v>
+        <v>0.06624942272901535</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.1034539267420769</v>
+        <v>0.05821219831705093</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.04843055084347725</v>
+        <v>0.1266501992940903</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.07278575748205185</v>
+        <v>0.03973089903593063</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.01954059675335884</v>
+        <v>0.01936562731862068</v>
       </c>
       <c r="FM15" t="n">
-        <v>0.2161252349615097</v>
+        <v>0.01228188909590244</v>
       </c>
       <c r="FN15" t="n">
-        <v>0.1019642204046249</v>
+        <v>0.1242107152938843</v>
       </c>
       <c r="FO15" t="n">
-        <v>0.130418598651886</v>
+        <v>0.0298125222325325</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.08288805931806564</v>
+        <v>0.2351099401712418</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.005262302234768867</v>
+        <v>0.3585720956325531</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.140032172203064</v>
+        <v>0.08186381310224533</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.2098635137081146</v>
+        <v>0.1135227903723717</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.1955044120550156</v>
+        <v>0.1540813744068146</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.02928456850349903</v>
+        <v>0.2102181017398834</v>
       </c>
       <c r="FV15" t="n">
-        <v>0.21839839220047</v>
+        <v>0.1700832098722458</v>
       </c>
       <c r="FW15" t="n">
-        <v>0.2366896569728851</v>
+        <v>0.1075810641050339</v>
       </c>
       <c r="FX15" t="n">
-        <v>0.06669491529464722</v>
+        <v>0.3226118087768555</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.05754196271300316</v>
+        <v>0.198787197470665</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.1460489630699158</v>
+        <v>0.07233799248933792</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.02732955291867256</v>
+        <v>0.0102265477180481</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.1176359057426453</v>
+        <v>0.006918819155544043</v>
       </c>
       <c r="GC15" t="n">
-        <v>0.04518990591168404</v>
+        <v>0.06583202630281448</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.1283501237630844</v>
+        <v>0.05639312416315079</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.1664988249540329</v>
+        <v>0.09658183157444</v>
       </c>
       <c r="GF15" t="n">
-        <v>0.4628685712814331</v>
+        <v>0.05062541738152504</v>
       </c>
       <c r="GG15" t="n">
-        <v>0.00286285113543272</v>
+        <v>0.01682428084313869</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.0002468930324539542</v>
+        <v>0.0001979006774490699</v>
       </c>
       <c r="B16" t="n">
-        <v>0.002462376840412617</v>
+        <v>0.00309496489353478</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0002888723684009165</v>
+        <v>0.0003195802273694426</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0007935849134810269</v>
+        <v>0.001475456985644996</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0006208957638591528</v>
+        <v>0.0005568781634792686</v>
       </c>
       <c r="F16" t="n">
-        <v>0.001208536792546511</v>
+        <v>0.003238030709326267</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0002334644959773868</v>
+        <v>0.0006710814195685089</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0007758846622891724</v>
+        <v>0.002694719471037388</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0002458417729940265</v>
+        <v>0.0004854728176724166</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0003788500907830894</v>
+        <v>0.0004406894440762699</v>
       </c>
       <c r="K16" t="n">
-        <v>0.002387359039857984</v>
+        <v>0.003319841343909502</v>
       </c>
       <c r="L16" t="n">
-        <v>8.485480793751776e-05</v>
+        <v>0.001260519959032536</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0004764671029988676</v>
+        <v>0.002747850026935339</v>
       </c>
       <c r="N16" t="n">
-        <v>2.368018613196909e-06</v>
+        <v>0.001817325362935662</v>
       </c>
       <c r="O16" t="n">
-        <v>0.001334661967121065</v>
+        <v>0.004009883385151625</v>
       </c>
       <c r="P16" t="n">
-        <v>0.0001368097146041691</v>
+        <v>0.0003231404407415539</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0002263708738610148</v>
+        <v>0.001825989689677954</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0001052419029292651</v>
+        <v>0.0001661819260334596</v>
       </c>
       <c r="S16" t="n">
-        <v>5.646409772452898e-05</v>
+        <v>5.21922847838141e-05</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0002519271220080554</v>
+        <v>0.0005002877442166209</v>
       </c>
       <c r="U16" t="n">
-        <v>5.656799476128072e-05</v>
+        <v>0.0004674936644732952</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0003955483552999794</v>
+        <v>0.0001878082111943513</v>
       </c>
       <c r="W16" t="n">
-        <v>0.000241660134634003</v>
+        <v>0.0004774818662554026</v>
       </c>
       <c r="X16" t="n">
-        <v>1.874908775789663e-06</v>
+        <v>0.0006870808429084718</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.614717570599169e-06</v>
+        <v>0.0005298159085214138</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.0002850081073120236</v>
+        <v>0.0005023522535338998</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.585330654866993e-05</v>
+        <v>0.0003228961140848696</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.0001105003320844844</v>
+        <v>0.0001348067307844758</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.0001465787354391068</v>
+        <v>0.0004001958877779543</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.0001093443715944886</v>
+        <v>0.0001696005056146532</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.0001442198699805886</v>
+        <v>0.0009324739221483469</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.0001729884825181216</v>
+        <v>0.0007859716424718499</v>
       </c>
       <c r="AG16" t="n">
-        <v>7.194955833256245e-05</v>
+        <v>0.001332139363512397</v>
       </c>
       <c r="AH16" t="n">
-        <v>5.454168785945512e-05</v>
+        <v>0.000186150660738349</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.0002295021404279396</v>
+        <v>0.002317874226719141</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.0001716510305413976</v>
+        <v>0.0001360863534500822</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.0004168377490714192</v>
+        <v>0.0001706404727883637</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.0001720565196592361</v>
+        <v>0.0004161107062827796</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.441486438125139e-05</v>
+        <v>0.0004050609713885933</v>
       </c>
       <c r="AN16" t="n">
-        <v>3.464408655418083e-05</v>
+        <v>0.0002560763678047806</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.0001383631170028821</v>
+        <v>0.0007010578410699964</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.0003798496327362955</v>
+        <v>0.000376214535208419</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.0001226677850354463</v>
+        <v>0.0001802127080736682</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.0002224703202955425</v>
+        <v>0.0008623324101790786</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.0002587616036180407</v>
+        <v>0.0002611591480672359</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.000120211741887033</v>
+        <v>0.000401878118282184</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.001344235381111503</v>
+        <v>0.003580913413316011</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.0003991677949670702</v>
+        <v>0.0007982599199749529</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.0001528371503809467</v>
+        <v>0.0009701859671622515</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.0003512547991704196</v>
+        <v>0.002285538474097848</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.0004045859386678785</v>
+        <v>0.002893506782129407</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.0002059527614619583</v>
+        <v>0.0001820478209992871</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.000307410373352468</v>
+        <v>0.0005791147123090923</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.115110151469707e-05</v>
+        <v>0.0004632884520106018</v>
       </c>
       <c r="BC16" t="n">
-        <v>0.0001469721464673057</v>
+        <v>0.0004369959351606667</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.0006226036930456758</v>
+        <v>0.0005227732472121716</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.0007464677910320461</v>
+        <v>0.0004975979682058096</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.437151695427019e-05</v>
+        <v>0.0005773083539679646</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.166177288629115e-05</v>
+        <v>0.0007826854707673192</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.0003403870505280793</v>
+        <v>0.0002686075458768755</v>
       </c>
       <c r="BI16" t="n">
-        <v>0.0002590058138594031</v>
+        <v>5.388428689911962e-05</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.000123902180348523</v>
+        <v>0.001776541816070676</v>
       </c>
       <c r="BK16" t="n">
-        <v>7.990666199475527e-05</v>
+        <v>0.0002152548549929634</v>
       </c>
       <c r="BL16" t="n">
-        <v>9.24554406083189e-05</v>
+        <v>0.000419579679146409</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.0002965685271192342</v>
+        <v>0.001172954449430108</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.0003057034045923501</v>
+        <v>0.000678007781971246</v>
       </c>
       <c r="BO16" t="n">
-        <v>7.798878505127504e-05</v>
+        <v>0.0002804191608447582</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.0001976917556021363</v>
+        <v>0.0004567583673633635</v>
       </c>
       <c r="BQ16" t="n">
-        <v>8.641777094453573e-05</v>
+        <v>0.0003191189316567034</v>
       </c>
       <c r="BR16" t="n">
-        <v>0.0001835443690652028</v>
+        <v>0.000811901583801955</v>
       </c>
       <c r="BS16" t="n">
-        <v>0.0001439315674360842</v>
+        <v>0.0007744184113107622</v>
       </c>
       <c r="BT16" t="n">
-        <v>0.0003722895635291934</v>
+        <v>0.0004480138886719942</v>
       </c>
       <c r="BU16" t="n">
-        <v>7.678634574403986e-06</v>
+        <v>1.96618857444264e-05</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.0008095044177025557</v>
+        <v>0.001770961680449545</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.0002033750643022358</v>
+        <v>0.0004133639740757644</v>
       </c>
       <c r="BX16" t="n">
-        <v>6.183474033605307e-05</v>
+        <v>0.0006011652876622975</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.0001381319889333099</v>
+        <v>0.0006244863034226</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.0002849657903425395</v>
+        <v>0.001425159280188382</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.560423985822126e-05</v>
+        <v>0.0006580806220881641</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.0001346895151073113</v>
+        <v>0.0003502359322737902</v>
       </c>
       <c r="CC16" t="n">
-        <v>1.107275238609873e-05</v>
+        <v>0.0004249641788192093</v>
       </c>
       <c r="CD16" t="n">
-        <v>9.571576811140403e-05</v>
+        <v>6.26144465059042e-05</v>
       </c>
       <c r="CE16" t="n">
-        <v>0.0004641395935323089</v>
+        <v>0.00100428075529635</v>
       </c>
       <c r="CF16" t="n">
-        <v>0.0001657993707340211</v>
+        <v>0.0003638721245806664</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.0001382129994453862</v>
+        <v>0.000396782299503684</v>
       </c>
       <c r="CH16" t="n">
-        <v>8.562512812204659e-05</v>
+        <v>0.0004674348165281117</v>
       </c>
       <c r="CI16" t="n">
-        <v>8.086537854978815e-05</v>
+        <v>0.0007516878540627658</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0.0001545588311273605</v>
+        <v>5.881060496903956e-05</v>
       </c>
       <c r="CK16" t="n">
-        <v>0.000182122370461002</v>
+        <v>0.0002618650323711336</v>
       </c>
       <c r="CL16" t="n">
-        <v>0.0001251114736078307</v>
+        <v>0.0002161295706173405</v>
       </c>
       <c r="CM16" t="n">
-        <v>0.0006403104634955525</v>
+        <v>0.0004391283146105707</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.0002862589317373931</v>
+        <v>0.001603711396455765</v>
       </c>
       <c r="CO16" t="n">
-        <v>2.595136174932122e-05</v>
+        <v>0.001664108131080866</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.0004036907339468598</v>
+        <v>0.001238627824932337</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.0003997112798970193</v>
+        <v>0.0008837392088025808</v>
       </c>
       <c r="CR16" t="n">
-        <v>0.0006628257688134909</v>
+        <v>0.0001486825640313327</v>
       </c>
       <c r="CS16" t="n">
-        <v>0.0004188479506410658</v>
+        <v>0.0002884310088120401</v>
       </c>
       <c r="CT16" t="n">
-        <v>0.0002415268972981721</v>
+        <v>0.0003324571589473635</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.913347477966454e-05</v>
+        <v>0.0005478006787598133</v>
       </c>
       <c r="CV16" t="n">
-        <v>9.289983427152038e-05</v>
+        <v>0.0002771838626358658</v>
       </c>
       <c r="CW16" t="n">
-        <v>0.0004504345415625721</v>
+        <v>0.0007827400113455951</v>
       </c>
       <c r="CX16" t="n">
-        <v>0.0001951318845385686</v>
+        <v>0.0004480289644561708</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.0002461093536112458</v>
+        <v>0.0006128927343524992</v>
       </c>
       <c r="CZ16" t="n">
-        <v>7.395417924271896e-05</v>
+        <v>0.0003872732049785554</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.0001066484546754509</v>
+        <v>0.0009473242680542171</v>
       </c>
       <c r="DB16" t="n">
-        <v>0.0001471024006605148</v>
+        <v>3.319921597721986e-05</v>
       </c>
       <c r="DC16" t="n">
-        <v>0.0002738381735980511</v>
+        <v>0.0001793743140297011</v>
       </c>
       <c r="DD16" t="n">
-        <v>0.0001074417523341253</v>
+        <v>6.407517503248528e-05</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.0002125453902408481</v>
+        <v>0.0001689645287115127</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.0001897940674098209</v>
+        <v>0.001216073986142874</v>
       </c>
       <c r="DG16" t="n">
-        <v>9.130072612606455e-06</v>
+        <v>0.001097538974136114</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.0006803912692703307</v>
+        <v>5.586087354458869e-06</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.001022580312564969</v>
+        <v>0.00028220284730196</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.0002368215064052492</v>
+        <v>0.00146174686960876</v>
       </c>
       <c r="DK16" t="n">
-        <v>0.0001374108251184225</v>
+        <v>0.0001717810228001326</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.0003212492156308144</v>
+        <v>0.0008454946801066399</v>
       </c>
       <c r="DM16" t="n">
-        <v>0.0004086460685357451</v>
+        <v>5.873338159290142e-05</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.0001542673853691667</v>
+        <v>3.667494092951529e-05</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.0002969201887026429</v>
+        <v>0.0002298045292263851</v>
       </c>
       <c r="DP16" t="n">
-        <v>0.000156627400428988</v>
+        <v>0.0002383957616984844</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0.0001621415140107274</v>
+        <v>0.0002568999771028757</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.0001479436905356124</v>
+        <v>0.000519462046213448</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.0002006086579058319</v>
+        <v>0.0005710871773771942</v>
       </c>
       <c r="DT16" t="n">
-        <v>8.497626549797133e-05</v>
+        <v>0.0005559282726608217</v>
       </c>
       <c r="DU16" t="n">
-        <v>0.0003053632099181414</v>
+        <v>0.0007573531474918127</v>
       </c>
       <c r="DV16" t="n">
-        <v>6.40998114249669e-05</v>
+        <v>0.0004607816808857024</v>
       </c>
       <c r="DW16" t="n">
-        <v>3.495149576338008e-05</v>
+        <v>0.0001960449881153181</v>
       </c>
       <c r="DX16" t="n">
-        <v>0.0002653342671692371</v>
+        <v>0.0001150196621892974</v>
       </c>
       <c r="DY16" t="n">
-        <v>0.0001602985139470547</v>
+        <v>0.000618590391241014</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.0001428979885531589</v>
+        <v>2.622345346026123e-05</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.0002340428764000535</v>
+        <v>0.0003912339743692428</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.812467235140502e-05</v>
+        <v>1.665016316110268e-05</v>
       </c>
       <c r="EC16" t="n">
-        <v>0.0001301860029343516</v>
+        <v>6.526734796352684e-05</v>
       </c>
       <c r="ED16" t="n">
-        <v>5.744284862885252e-06</v>
+        <v>0.001318803755566478</v>
       </c>
       <c r="EE16" t="n">
-        <v>0.0002246953081339598</v>
+        <v>0.001699479878880084</v>
       </c>
       <c r="EF16" t="n">
-        <v>0.0003748093149624765</v>
+        <v>1.428781979484484e-05</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.0006079634185880423</v>
+        <v>0.0004423086065798998</v>
       </c>
       <c r="EH16" t="n">
-        <v>0.0002631340175867081</v>
+        <v>1.127048744820058e-05</v>
       </c>
       <c r="EI16" t="n">
-        <v>0.000163187287398614</v>
+        <v>0.0005627026548609138</v>
       </c>
       <c r="EJ16" t="n">
-        <v>2.604399924166501e-05</v>
+        <v>0.0002548415213823318</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.0001393653947161511</v>
+        <v>0.0005136476247571409</v>
       </c>
       <c r="EL16" t="n">
-        <v>0.0001136658975156024</v>
+        <v>6.637787009822205e-06</v>
       </c>
       <c r="EM16" t="n">
-        <v>0.0001300689909840003</v>
+        <v>0.0004955537733621895</v>
       </c>
       <c r="EN16" t="n">
-        <v>3.0156945285853e-05</v>
+        <v>0.0002065533917630091</v>
       </c>
       <c r="EO16" t="n">
-        <v>0.0001021370117086917</v>
+        <v>0.00051203987095505</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.0001423398207407445</v>
+        <v>0.0009992283303290606</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0.0002353079325985163</v>
+        <v>0.0006168847903609276</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.0002456329530104995</v>
+        <v>0.0006194048328325152</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.0001111038072849624</v>
+        <v>0.0001077419437933713</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.0003419909626245499</v>
+        <v>0.0004568061849568039</v>
       </c>
       <c r="EU16" t="n">
-        <v>0.0002720812044572085</v>
+        <v>0.000199806148884818</v>
       </c>
       <c r="EV16" t="n">
-        <v>0.0004808931553270668</v>
+        <v>6.988542736507952e-05</v>
       </c>
       <c r="EW16" t="n">
-        <v>0.0001157431615865789</v>
+        <v>0.000301285763271153</v>
       </c>
       <c r="EX16" t="n">
-        <v>0.0001384201023029163</v>
+        <v>0.0001873173314379528</v>
       </c>
       <c r="EY16" t="n">
-        <v>0.0004293781530577689</v>
+        <v>0.001187383662909269</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0.0001724301837384701</v>
+        <v>0.0002688350796233863</v>
       </c>
       <c r="FA16" t="n">
-        <v>0.000105387982330285</v>
+        <v>0.0006293858750723302</v>
       </c>
       <c r="FB16" t="n">
-        <v>6.814111111452803e-05</v>
+        <v>0.0002990481443703175</v>
       </c>
       <c r="FC16" t="n">
-        <v>8.64110843394883e-05</v>
+        <v>0.0008228315273299813</v>
       </c>
       <c r="FD16" t="n">
-        <v>0.0001853363064583391</v>
+        <v>0.000167275924468413</v>
       </c>
       <c r="FE16" t="n">
-        <v>0.000252633064519614</v>
+        <v>0.0001636232482269406</v>
       </c>
       <c r="FF16" t="n">
-        <v>0.0001310857769567519</v>
+        <v>2.219565431005321e-05</v>
       </c>
       <c r="FG16" t="n">
-        <v>0.0001353069819742814</v>
+        <v>6.658793427050114e-05</v>
       </c>
       <c r="FH16" t="n">
-        <v>0.0001288517960347235</v>
+        <v>0.0007173271733336151</v>
       </c>
       <c r="FI16" t="n">
-        <v>0.000339621416060254</v>
+        <v>0.0005555744864977896</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.0002570674987509847</v>
+        <v>0.0005791031289845705</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.0002118379343301058</v>
+        <v>0.0008046862203627825</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.0003151168348267674</v>
+        <v>0.0009102468611672521</v>
       </c>
       <c r="FM16" t="n">
-        <v>2.921481791418046e-05</v>
+        <v>0.0004055164172314107</v>
       </c>
       <c r="FN16" t="n">
-        <v>0.0001521008380223066</v>
+        <v>0.0005002807010896504</v>
       </c>
       <c r="FO16" t="n">
-        <v>0.0001383402559440583</v>
+        <v>0.00204085698351264</v>
       </c>
       <c r="FP16" t="n">
-        <v>0.0003727457951754332</v>
+        <v>0.0002044970024144277</v>
       </c>
       <c r="FQ16" t="n">
-        <v>5.793038144474849e-05</v>
+        <v>0.0006034944672137499</v>
       </c>
       <c r="FR16" t="n">
-        <v>0.0005804885877296329</v>
+        <v>0.0004950815346091986</v>
       </c>
       <c r="FS16" t="n">
-        <v>0.0001603289856575429</v>
+        <v>0.0002781847724691033</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.000233063503401354</v>
+        <v>0.001503334729932249</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.0001332109386567026</v>
+        <v>0.0003976174630224705</v>
       </c>
       <c r="FV16" t="n">
-        <v>8.30375065561384e-05</v>
+        <v>2.077280078083277e-05</v>
       </c>
       <c r="FW16" t="n">
-        <v>0.0001503016101196408</v>
+        <v>0.002671183086931705</v>
       </c>
       <c r="FX16" t="n">
-        <v>3.184549132129177e-05</v>
+        <v>0.000322725682053715</v>
       </c>
       <c r="FY16" t="n">
-        <v>0.0004414279828779399</v>
+        <v>0.0004428969987202436</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.0002065214066533372</v>
+        <v>0.0006889727665111423</v>
       </c>
       <c r="GA16" t="n">
-        <v>0.0001473756419727579</v>
+        <v>0.001625494565814734</v>
       </c>
       <c r="GB16" t="n">
-        <v>2.710589615162462e-05</v>
+        <v>0.000309815164655447</v>
       </c>
       <c r="GC16" t="n">
-        <v>9.128890087595209e-05</v>
+        <v>0.001638703164644539</v>
       </c>
       <c r="GD16" t="n">
-        <v>0.0002630789240356535</v>
+        <v>0.001220683567225933</v>
       </c>
       <c r="GE16" t="n">
-        <v>0.0003859320131596178</v>
+        <v>0.0006756890215910971</v>
       </c>
       <c r="GF16" t="n">
-        <v>0.0001066746335709468</v>
+        <v>0.0001711145741865039</v>
       </c>
       <c r="GG16" t="n">
-        <v>0.0003594165900722146</v>
+        <v>3.135254883090965e-05</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.0001036732573993504</v>
+        <v>0.005778203718364239</v>
       </c>
       <c r="B17" t="n">
-        <v>0.001063052914105356</v>
+        <v>0.006686939857900143</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0001246274478035048</v>
+        <v>0.003288706298917532</v>
       </c>
       <c r="D17" t="n">
-        <v>0.000382688594982028</v>
+        <v>0.0015077143907547</v>
       </c>
       <c r="E17" t="n">
-        <v>3.340434705023654e-05</v>
+        <v>0.0125732971355319</v>
       </c>
       <c r="F17" t="n">
-        <v>0.001336193992756307</v>
+        <v>0.02025982551276684</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0003109711688011885</v>
+        <v>0.004594277590513229</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0007145433919504285</v>
+        <v>0.01601266302168369</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0002463384007569402</v>
+        <v>0.001162024447694421</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0002267982927151024</v>
+        <v>0.003677161410450935</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0007996504427865148</v>
+        <v>0.01337309926748276</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0002582015586085618</v>
+        <v>0.008135005831718445</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0003334557986818254</v>
+        <v>0.006717569194734097</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0001205987355206162</v>
+        <v>0.01779183000326157</v>
       </c>
       <c r="O17" t="n">
-        <v>0.001109027885831892</v>
+        <v>0.02839005924761295</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0002211731625720859</v>
+        <v>0.002689554821699858</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.0004945586551912129</v>
+        <v>0.01040532719343901</v>
       </c>
       <c r="R17" t="n">
-        <v>0.0001664938754402101</v>
+        <v>0.005829448346048594</v>
       </c>
       <c r="S17" t="n">
-        <v>6.042440872988664e-05</v>
+        <v>0.00277158641256392</v>
       </c>
       <c r="T17" t="n">
-        <v>2.355009200982749e-05</v>
+        <v>0.002696814946830273</v>
       </c>
       <c r="U17" t="n">
-        <v>8.652474207337946e-05</v>
+        <v>0.004244787618517876</v>
       </c>
       <c r="V17" t="n">
-        <v>9.547959052724764e-05</v>
+        <v>0.006415582727640867</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0002777580812107772</v>
+        <v>0.003975235391408205</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0001424487854819745</v>
+        <v>0.003139623440802097</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.0001209900001413189</v>
+        <v>0.002432164503261447</v>
       </c>
       <c r="Z17" t="n">
-        <v>8.97471618372947e-05</v>
+        <v>0.007037817966192961</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.111749123898335e-05</v>
+        <v>0.002015922451391816</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.016399078769609e-06</v>
+        <v>0.003243836108595133</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.0001260818971786648</v>
+        <v>0.004730297718197107</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.0002610941010061651</v>
+        <v>0.0008805853431113064</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.0001840212935348973</v>
+        <v>0.006705923937261105</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.0002413140318822116</v>
+        <v>0.01051500998437405</v>
       </c>
       <c r="AG17" t="n">
-        <v>9.018143464345485e-05</v>
+        <v>0.004892164375633001</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.0001328183279838413</v>
+        <v>0.001327809644863009</v>
       </c>
       <c r="AI17" t="n">
-        <v>7.972898310981691e-05</v>
+        <v>0.01002664864063263</v>
       </c>
       <c r="AJ17" t="n">
-        <v>8.227398211602122e-05</v>
+        <v>0.002880732994526625</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.0001556470815557986</v>
+        <v>0.004945944994688034</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.407210922683589e-05</v>
+        <v>0.003123662900179625</v>
       </c>
       <c r="AM17" t="n">
-        <v>2.980568388011307e-05</v>
+        <v>0.00104812323115766</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.04199607449118e-05</v>
+        <v>0.0008497122908011079</v>
       </c>
       <c r="AO17" t="n">
-        <v>6.980514444876462e-05</v>
+        <v>0.003917684778571129</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.0002045149158220738</v>
+        <v>0.002975981682538986</v>
       </c>
       <c r="AQ17" t="n">
-        <v>7.911838110885583e-06</v>
+        <v>0.005756259895861149</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.0001192021300084889</v>
+        <v>0.007207203190773726</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.478209979832172e-05</v>
+        <v>0.001083834911696613</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.0001734847610350698</v>
+        <v>0.005999602843075991</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.0006968794041313231</v>
+        <v>0.0286150723695755</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.602551780408248e-05</v>
+        <v>0.0009831583593040705</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.0003979591419920325</v>
+        <v>0.001633700681850314</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.0004276700201444328</v>
+        <v>0.0007107225828804076</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.0007576015777885914</v>
+        <v>0.02234701067209244</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.0001649060286581516</v>
+        <v>0.00496241357177496</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.0001481575745856389</v>
+        <v>0.004706043284386396</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.0001248513581231236</v>
+        <v>0.001026870217174292</v>
       </c>
       <c r="BC17" t="n">
-        <v>9.595701703801751e-05</v>
+        <v>0.003470175433903933</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.0002756783505901694</v>
+        <v>0.00808256771415472</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.000227639771765098</v>
+        <v>0.002786905271932483</v>
       </c>
       <c r="BF17" t="n">
-        <v>7.86119926488027e-06</v>
+        <v>0.009540409781038761</v>
       </c>
       <c r="BG17" t="n">
-        <v>6.385124288499355e-05</v>
+        <v>0.007095509674400091</v>
       </c>
       <c r="BH17" t="n">
-        <v>0.0003022102755494416</v>
+        <v>0.002707571256905794</v>
       </c>
       <c r="BI17" t="n">
-        <v>0.000190742954146117</v>
+        <v>0.003204982727766037</v>
       </c>
       <c r="BJ17" t="n">
-        <v>8.768741099629551e-05</v>
+        <v>0.006865967996418476</v>
       </c>
       <c r="BK17" t="n">
-        <v>7.419962639687583e-05</v>
+        <v>0.003199158003553748</v>
       </c>
       <c r="BL17" t="n">
-        <v>2.267685340484604e-05</v>
+        <v>0.0008285914082080126</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.0003264068509452045</v>
+        <v>0.007842644117772579</v>
       </c>
       <c r="BN17" t="n">
-        <v>5.676376531482674e-05</v>
+        <v>0.005393244326114655</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.0001240966230398044</v>
+        <v>0.002657745964825153</v>
       </c>
       <c r="BP17" t="n">
-        <v>1.28177744045388e-05</v>
+        <v>0.006156228948384523</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.54977387865074e-05</v>
+        <v>0.002015429781749845</v>
       </c>
       <c r="BR17" t="n">
-        <v>8.947990136221051e-05</v>
+        <v>0.01003088057041168</v>
       </c>
       <c r="BS17" t="n">
-        <v>5.627906284644268e-05</v>
+        <v>0.002418098039925098</v>
       </c>
       <c r="BT17" t="n">
-        <v>3.603059303713962e-05</v>
+        <v>0.00612877681851387</v>
       </c>
       <c r="BU17" t="n">
-        <v>7.209582690848038e-05</v>
+        <v>0.001907361554913223</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.0003314850619062781</v>
+        <v>0.01223658956587315</v>
       </c>
       <c r="BW17" t="n">
-        <v>3.159724292345345e-05</v>
+        <v>0.001595032168552279</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.000165984543855302</v>
+        <v>0.001632132101804018</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.0001962981768883765</v>
+        <v>0.001221915706992149</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.0004350215895101428</v>
+        <v>0.01102423295378685</v>
       </c>
       <c r="CA17" t="n">
-        <v>0.0001303118333453313</v>
+        <v>0.002385162748396397</v>
       </c>
       <c r="CB17" t="n">
-        <v>5.3953226597514e-05</v>
+        <v>0.003934658598154783</v>
       </c>
       <c r="CC17" t="n">
-        <v>8.50030301080551e-06</v>
+        <v>0.0006105127977207303</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.898831189668272e-05</v>
+        <v>0.002593235112726688</v>
       </c>
       <c r="CE17" t="n">
-        <v>0.0001044682139763609</v>
+        <v>0.002868169918656349</v>
       </c>
       <c r="CF17" t="n">
-        <v>4.282861846149899e-05</v>
+        <v>0.001757921185344458</v>
       </c>
       <c r="CG17" t="n">
-        <v>1.945902295119595e-05</v>
+        <v>0.0007044889498502016</v>
       </c>
       <c r="CH17" t="n">
-        <v>3.130446202703752e-06</v>
+        <v>0.002542171627283096</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.0002268482639919966</v>
+        <v>0.006286379881203175</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.150415457435884e-05</v>
+        <v>0.003942064009606838</v>
       </c>
       <c r="CK17" t="n">
-        <v>0.0001025079036480747</v>
+        <v>0.0004037469625473022</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.029819188464899e-05</v>
+        <v>0.002032983815297484</v>
       </c>
       <c r="CM17" t="n">
-        <v>0.0001654248626437038</v>
+        <v>0.005529762245714664</v>
       </c>
       <c r="CN17" t="n">
-        <v>0.0001007713362923823</v>
+        <v>0.01354107074439526</v>
       </c>
       <c r="CO17" t="n">
-        <v>3.180278145009652e-05</v>
+        <v>0.00264481152407825</v>
       </c>
       <c r="CP17" t="n">
-        <v>5.490457988344133e-05</v>
+        <v>0.006240156013518572</v>
       </c>
       <c r="CQ17" t="n">
-        <v>0.000291357486275956</v>
+        <v>0.0026332619599998</v>
       </c>
       <c r="CR17" t="n">
-        <v>3.384777664905414e-05</v>
+        <v>0.008396345190703869</v>
       </c>
       <c r="CS17" t="n">
-        <v>3.55985393980518e-05</v>
+        <v>0.001519196317531168</v>
       </c>
       <c r="CT17" t="n">
-        <v>0.0002171778469346464</v>
+        <v>7.703120354562998e-05</v>
       </c>
       <c r="CU17" t="n">
-        <v>3.573133653844707e-06</v>
+        <v>0.0001753264223225415</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.238832555827685e-05</v>
+        <v>0.002968387678265572</v>
       </c>
       <c r="CW17" t="n">
-        <v>8.310877456096932e-05</v>
+        <v>0.002435576636344194</v>
       </c>
       <c r="CX17" t="n">
-        <v>2.592895179986954e-05</v>
+        <v>0.00134477368555963</v>
       </c>
       <c r="CY17" t="n">
-        <v>6.025476614013314e-05</v>
+        <v>0.0005437179352156818</v>
       </c>
       <c r="CZ17" t="n">
-        <v>3.196529360138811e-05</v>
+        <v>0.003197928890585899</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.0002161586162401363</v>
+        <v>0.007284563034772873</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.545994746265933e-05</v>
+        <v>0.00140235130675137</v>
       </c>
       <c r="DC17" t="n">
-        <v>0.0001227227912750095</v>
+        <v>0.001446185517124832</v>
       </c>
       <c r="DD17" t="n">
-        <v>9.246374247595668e-05</v>
+        <v>0.002061153529211879</v>
       </c>
       <c r="DE17" t="n">
-        <v>3.808482870226726e-05</v>
+        <v>0.004244952462613583</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.0002409126318525523</v>
+        <v>0.00052653718739748</v>
       </c>
       <c r="DG17" t="n">
-        <v>6.376889359671623e-06</v>
+        <v>0.0001377196749672294</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.000401507830247283</v>
+        <v>0.003070962149649858</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.0001769577356753871</v>
+        <v>0.003648141631856561</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.21608133870177e-05</v>
+        <v>0.002580818254500628</v>
       </c>
       <c r="DK17" t="n">
-        <v>0.0001082062226487324</v>
+        <v>0.002115907613188028</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.0003874582471325994</v>
+        <v>0.002189919352531433</v>
       </c>
       <c r="DM17" t="n">
-        <v>0.0001302761666011065</v>
+        <v>0.002365614287555218</v>
       </c>
       <c r="DN17" t="n">
-        <v>4.784475822816603e-05</v>
+        <v>0.005001284182071686</v>
       </c>
       <c r="DO17" t="n">
-        <v>3.878783900290728e-05</v>
+        <v>0.004270107951015234</v>
       </c>
       <c r="DP17" t="n">
-        <v>8.277745655504987e-05</v>
+        <v>0.002208813093602657</v>
       </c>
       <c r="DQ17" t="n">
-        <v>0.0001194502401631325</v>
+        <v>0.004294720944017172</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.297984848264605e-05</v>
+        <v>0.00289009721018374</v>
       </c>
       <c r="DS17" t="n">
-        <v>1.789834186638473e-06</v>
+        <v>0.00339033454656601</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.0002312635042471811</v>
+        <v>0.002236205618828535</v>
       </c>
       <c r="DU17" t="n">
-        <v>2.62941794062499e-05</v>
+        <v>0.005251247435808182</v>
       </c>
       <c r="DV17" t="n">
-        <v>5.276582669466734e-05</v>
+        <v>0.005037661641836166</v>
       </c>
       <c r="DW17" t="n">
-        <v>4.15207032347098e-05</v>
+        <v>0.001793999224901199</v>
       </c>
       <c r="DX17" t="n">
-        <v>5.00440364703536e-05</v>
+        <v>0.007304645143449306</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.194184243213385e-05</v>
+        <v>0.00352051155641675</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.71311759611126e-05</v>
+        <v>0.002758955582976341</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.0001118519576266408</v>
+        <v>0.001145718968473375</v>
       </c>
       <c r="EB17" t="n">
-        <v>7.206317241070792e-05</v>
+        <v>0.005490279290825129</v>
       </c>
       <c r="EC17" t="n">
-        <v>0.0001070154685294256</v>
+        <v>0.0006531442049890757</v>
       </c>
       <c r="ED17" t="n">
-        <v>0.0001455165474908426</v>
+        <v>0.00438398402184248</v>
       </c>
       <c r="EE17" t="n">
-        <v>3.59794867108576e-05</v>
+        <v>0.0008555550593882799</v>
       </c>
       <c r="EF17" t="n">
-        <v>1.991396493394859e-05</v>
+        <v>0.0007746983901597559</v>
       </c>
       <c r="EG17" t="n">
-        <v>4.338128564995714e-05</v>
+        <v>0.001562145305797458</v>
       </c>
       <c r="EH17" t="n">
-        <v>2.789636164379772e-05</v>
+        <v>0.001373978331685066</v>
       </c>
       <c r="EI17" t="n">
-        <v>3.34047363139689e-05</v>
+        <v>0.0017546396702528</v>
       </c>
       <c r="EJ17" t="n">
-        <v>1.313005122938193e-05</v>
+        <v>0.004812471102923155</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.0001995357888517901</v>
+        <v>0.0002978970296680927</v>
       </c>
       <c r="EL17" t="n">
-        <v>3.451731754466891e-05</v>
+        <v>0.002727832179516554</v>
       </c>
       <c r="EM17" t="n">
-        <v>6.098051017033868e-06</v>
+        <v>0.0007893013535067439</v>
       </c>
       <c r="EN17" t="n">
-        <v>4.699236524174921e-05</v>
+        <v>0.001216622302308679</v>
       </c>
       <c r="EO17" t="n">
-        <v>5.91371936025098e-05</v>
+        <v>0.001460971310734749</v>
       </c>
       <c r="EP17" t="n">
-        <v>3.675971311167814e-05</v>
+        <v>0.001886314596049488</v>
       </c>
       <c r="EQ17" t="n">
-        <v>9.471019438933581e-05</v>
+        <v>0.001750023569911718</v>
       </c>
       <c r="ER17" t="n">
-        <v>3.555911098374054e-05</v>
+        <v>0.001644065836444497</v>
       </c>
       <c r="ES17" t="n">
-        <v>1.301452721236274e-05</v>
+        <v>0.003984794486314058</v>
       </c>
       <c r="ET17" t="n">
-        <v>9.33281407924369e-05</v>
+        <v>0.007540012244135141</v>
       </c>
       <c r="EU17" t="n">
-        <v>4.85220443806611e-05</v>
+        <v>0.004366441629827023</v>
       </c>
       <c r="EV17" t="n">
-        <v>0.0003350286278873682</v>
+        <v>0.0006216707406565547</v>
       </c>
       <c r="EW17" t="n">
-        <v>0.0002159519935958087</v>
+        <v>0.00239220168441534</v>
       </c>
       <c r="EX17" t="n">
-        <v>1.231807709700661e-05</v>
+        <v>0.003644810989499092</v>
       </c>
       <c r="EY17" t="n">
-        <v>5.737557876273058e-05</v>
+        <v>0.004132329486310482</v>
       </c>
       <c r="EZ17" t="n">
-        <v>8.751863788347691e-06</v>
+        <v>0.0006117522134445608</v>
       </c>
       <c r="FA17" t="n">
-        <v>2.819784822349902e-05</v>
+        <v>0.00100483768619597</v>
       </c>
       <c r="FB17" t="n">
-        <v>1.783106927177869e-05</v>
+        <v>0.002082254271954298</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.0001996620703721419</v>
+        <v>0.006720634642988443</v>
       </c>
       <c r="FD17" t="n">
-        <v>7.214923243736848e-05</v>
+        <v>0.003598032984882593</v>
       </c>
       <c r="FE17" t="n">
-        <v>0.000105859333416447</v>
+        <v>0.0007881658966653049</v>
       </c>
       <c r="FF17" t="n">
-        <v>6.035608384991065e-05</v>
+        <v>0.001499369274824858</v>
       </c>
       <c r="FG17" t="n">
-        <v>4.145609273109585e-05</v>
+        <v>0.002005463466048241</v>
       </c>
       <c r="FH17" t="n">
-        <v>9.720709203975275e-05</v>
+        <v>0.002984375227242708</v>
       </c>
       <c r="FI17" t="n">
-        <v>0.0001559396769152954</v>
+        <v>0.0003062705509364605</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.0001475892495363951</v>
+        <v>0.003704079426825047</v>
       </c>
       <c r="FK17" t="n">
-        <v>6.74084949423559e-05</v>
+        <v>0.0001911025028675795</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.000193270345334895</v>
+        <v>0.006768936291337013</v>
       </c>
       <c r="FM17" t="n">
-        <v>5.196077836444601e-06</v>
+        <v>0.003843385027721524</v>
       </c>
       <c r="FN17" t="n">
-        <v>0.0001134593330789357</v>
+        <v>0.001540440367534757</v>
       </c>
       <c r="FO17" t="n">
-        <v>0.0002120151766575873</v>
+        <v>0.007034715730696917</v>
       </c>
       <c r="FP17" t="n">
-        <v>0.0001774091215338558</v>
+        <v>0.004461266100406647</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.0002576988190412521</v>
+        <v>0.004768525250256062</v>
       </c>
       <c r="FR17" t="n">
-        <v>2.336855504836421e-05</v>
+        <v>0.005860905162990093</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.0001201653576572426</v>
+        <v>0.01071632839739323</v>
       </c>
       <c r="FT17" t="n">
-        <v>3.297943476354703e-05</v>
+        <v>0.01611263304948807</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.0003044089826289564</v>
+        <v>0.0005660856841132045</v>
       </c>
       <c r="FV17" t="n">
-        <v>0.0001214212315971963</v>
+        <v>0.003092893864959478</v>
       </c>
       <c r="FW17" t="n">
-        <v>0.0001234320370713249</v>
+        <v>0.002303758636116982</v>
       </c>
       <c r="FX17" t="n">
-        <v>0.0002298981999047101</v>
+        <v>0.01123115979135036</v>
       </c>
       <c r="FY17" t="n">
-        <v>0.0001087659475160763</v>
+        <v>0.005376541987061501</v>
       </c>
       <c r="FZ17" t="n">
-        <v>7.53893400542438e-05</v>
+        <v>0.003091271733865142</v>
       </c>
       <c r="GA17" t="n">
-        <v>6.643750384682789e-05</v>
+        <v>0.0007737369742244482</v>
       </c>
       <c r="GB17" t="n">
-        <v>6.670139555353671e-06</v>
+        <v>0.002216069959104061</v>
       </c>
       <c r="GC17" t="n">
-        <v>0.0005807994166389108</v>
+        <v>0.00565269123762846</v>
       </c>
       <c r="GD17" t="n">
-        <v>0.0001064730240614153</v>
+        <v>0.001675843028351665</v>
       </c>
       <c r="GE17" t="n">
-        <v>0.0001670782367000356</v>
+        <v>0.002964769722893834</v>
       </c>
       <c r="GF17" t="n">
-        <v>3.443622335908003e-05</v>
+        <v>0.003657993162050843</v>
       </c>
       <c r="GG17" t="n">
-        <v>0.0001710406795609742</v>
+        <v>0.001894628745503724</v>
       </c>
     </row>
   </sheetData>
